--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N320"/>
+  <dimension ref="A1:N324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17424,6 +17424,190 @@
       <c r="N320" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/45560176/2024-toyota-rav4-hybrid-xle-il-chicago-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="7" t="inlineStr">
+        <is>
+          <t>46067086</t>
+        </is>
+      </c>
+      <c r="B321" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C321" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D321" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E321" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F321" s="7" t="n"/>
+      <c r="G321" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H321" s="8" t="n"/>
+      <c r="I321" s="7" t="n"/>
+      <c r="J321" s="7" t="inlineStr"/>
+      <c r="K321" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L321" s="7" t="inlineStr"/>
+      <c r="M321" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-12 19:56:35 UTC</t>
+        </is>
+      </c>
+      <c r="N321" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46067086/2025-toyota-rav4-xle-ky-louisville</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="5" t="inlineStr">
+        <is>
+          <t>45961856</t>
+        </is>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D322" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E322" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F322" s="5" t="n"/>
+      <c r="G322" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" s="6" t="n"/>
+      <c r="I322" s="5" t="n"/>
+      <c r="J322" s="5" t="inlineStr"/>
+      <c r="K322" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L322" s="5" t="inlineStr"/>
+      <c r="M322" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12 19:56:35 UTC</t>
+        </is>
+      </c>
+      <c r="N322" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/45961856/2024-toyota-rav4-xle-premium-ma-freetown</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="7" t="inlineStr">
+        <is>
+          <t>45796556</t>
+        </is>
+      </c>
+      <c r="B323" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C323" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D323" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E323" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F323" s="7" t="n"/>
+      <c r="G323" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H323" s="8" t="n"/>
+      <c r="I323" s="7" t="n"/>
+      <c r="J323" s="7" t="inlineStr"/>
+      <c r="K323" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L323" s="7" t="inlineStr"/>
+      <c r="M323" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-12 19:56:35 UTC</t>
+        </is>
+      </c>
+      <c r="N323" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/45796556/2025-toyota-rav4-hybrid-xle-al-birmingham</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="5" t="inlineStr">
+        <is>
+          <t>41715626</t>
+        </is>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 PRIME XSE</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D324" s="6" t="inlineStr">
+        <is>
+          <t>Engine Start Program</t>
+        </is>
+      </c>
+      <c r="E324" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F324" s="5" t="n"/>
+      <c r="G324" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H324" s="6" t="n"/>
+      <c r="I324" s="5" t="n"/>
+      <c r="J324" s="5" t="inlineStr"/>
+      <c r="K324" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L324" s="5" t="inlineStr"/>
+      <c r="M324" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12 19:56:35 UTC</t>
+        </is>
+      </c>
+      <c r="N324" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/41715626/2024-toyota-rav4-prime-xse-ma-south-boston</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N330"/>
+  <dimension ref="A1:N333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17884,6 +17884,152 @@
       <c r="N330" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/41792336/2025-toyota-rav4-hybrid-xle-wa-spanaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="7" t="inlineStr">
+        <is>
+          <t>45590706</t>
+        </is>
+      </c>
+      <c r="B331" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID LE</t>
+        </is>
+      </c>
+      <c r="C331" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D331" s="8" t="inlineStr">
+        <is>
+          <t>Engine Start Program</t>
+        </is>
+      </c>
+      <c r="E331" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F331" s="7" t="n"/>
+      <c r="G331" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H331" s="8" t="n"/>
+      <c r="I331" s="7" t="n"/>
+      <c r="J331" s="7" t="inlineStr"/>
+      <c r="K331" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L331" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:00 UTC</t>
+        </is>
+      </c>
+      <c r="M331" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:00:26 UTC</t>
+        </is>
+      </c>
+      <c r="N331" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/45590706/clean-title-2025-toyota-rav4-hybrid-le-ut-salt-lake-city</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="5" t="inlineStr">
+        <is>
+          <t>79610185</t>
+        </is>
+      </c>
+      <c r="B332" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025 TOYOTA RAV4 XLE  </t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D332" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E332" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F332" s="5" t="n"/>
+      <c r="G332" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H332" s="6" t="n"/>
+      <c r="I332" s="5" t="n"/>
+      <c r="J332" s="5" t="inlineStr"/>
+      <c r="K332" s="5" t="inlineStr">
+        <is>
+          <t>✅ NLR</t>
+        </is>
+      </c>
+      <c r="L332" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 18:00 UTC</t>
+        </is>
+      </c>
+      <c r="M332" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:00:26 UTC</t>
+        </is>
+      </c>
+      <c r="N332" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/79610185/salvage-2025-toyota-rav4-xle-id-boise</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="7" t="inlineStr">
+        <is>
+          <t>45826906</t>
+        </is>
+      </c>
+      <c r="B333" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C333" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D333" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E333" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F333" s="7" t="n"/>
+      <c r="G333" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H333" s="8" t="n"/>
+      <c r="I333" s="7" t="n"/>
+      <c r="J333" s="7" t="inlineStr"/>
+      <c r="K333" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L333" s="7" t="inlineStr"/>
+      <c r="M333" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:00:26 UTC</t>
+        </is>
+      </c>
+      <c r="N333" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/45826906/2025-toyota-rav4-xle-fl-ocala</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N333"/>
+  <dimension ref="A1:N334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18030,6 +18030,52 @@
       <c r="N333" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/45826906/2025-toyota-rav4-xle-fl-ocala</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="5" t="inlineStr">
+        <is>
+          <t>46394176</t>
+        </is>
+      </c>
+      <c r="B334" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D334" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E334" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F334" s="5" t="n"/>
+      <c r="G334" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H334" s="6" t="n"/>
+      <c r="I334" s="5" t="n"/>
+      <c r="J334" s="5" t="inlineStr"/>
+      <c r="K334" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L334" s="5" t="inlineStr"/>
+      <c r="M334" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-14 05:03:03 UTC</t>
+        </is>
+      </c>
+      <c r="N334" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46394176/2025-toyota-rav4-xle-il-chicago-north</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N334"/>
+  <dimension ref="A1:N336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18076,6 +18076,98 @@
       <c r="N334" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/46394176/2025-toyota-rav4-xle-il-chicago-north</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="7" t="inlineStr">
+        <is>
+          <t>77350385</t>
+        </is>
+      </c>
+      <c r="B335" s="7" t="inlineStr">
+        <is>
+          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C335" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D335" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E335" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F335" s="7" t="n"/>
+      <c r="G335" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H335" s="8" t="n"/>
+      <c r="I335" s="7" t="n"/>
+      <c r="J335" s="7" t="inlineStr"/>
+      <c r="K335" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L335" s="7" t="inlineStr"/>
+      <c r="M335" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-14 19:17:53 UTC</t>
+        </is>
+      </c>
+      <c r="N335" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/77350385/2022-toyota-rav4-xle-premium-mo-sikeston</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="5" t="inlineStr">
+        <is>
+          <t>45978486</t>
+        </is>
+      </c>
+      <c r="B336" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D336" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E336" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F336" s="5" t="n"/>
+      <c r="G336" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H336" s="6" t="n"/>
+      <c r="I336" s="5" t="n"/>
+      <c r="J336" s="5" t="inlineStr"/>
+      <c r="K336" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L336" s="5" t="inlineStr"/>
+      <c r="M336" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-14 19:17:53 UTC</t>
+        </is>
+      </c>
+      <c r="N336" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/45978486/2024-toyota-rav4-xle-tx-houston-east</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N341"/>
+  <dimension ref="A1:N345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18402,6 +18402,190 @@
       <c r="N341" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/45652486/2024-toyota-rav4-xle-premium-ar-little-rock</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="5" t="inlineStr">
+        <is>
+          <t>46290676</t>
+        </is>
+      </c>
+      <c r="B342" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D342" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E342" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F342" s="5" t="n"/>
+      <c r="G342" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H342" s="6" t="n"/>
+      <c r="I342" s="5" t="n"/>
+      <c r="J342" s="5" t="inlineStr"/>
+      <c r="K342" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L342" s="5" t="inlineStr"/>
+      <c r="M342" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:59:42 UTC</t>
+        </is>
+      </c>
+      <c r="N342" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46290676/2024-toyota-rav4-xle-il-chicago-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="7" t="inlineStr">
+        <is>
+          <t>46093286</t>
+        </is>
+      </c>
+      <c r="B343" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C343" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D343" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E343" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F343" s="7" t="n"/>
+      <c r="G343" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H343" s="8" t="n"/>
+      <c r="I343" s="7" t="n"/>
+      <c r="J343" s="7" t="inlineStr"/>
+      <c r="K343" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L343" s="7" t="inlineStr"/>
+      <c r="M343" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:59:42 UTC</t>
+        </is>
+      </c>
+      <c r="N343" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46093286/2024-toyota-rav4-hybrid-xle-premium-pa-pittsburgh-north</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="5" t="inlineStr">
+        <is>
+          <t>45799576</t>
+        </is>
+      </c>
+      <c r="B344" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C344" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D344" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E344" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F344" s="5" t="n"/>
+      <c r="G344" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H344" s="6" t="n"/>
+      <c r="I344" s="5" t="n"/>
+      <c r="J344" s="5" t="inlineStr"/>
+      <c r="K344" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L344" s="5" t="inlineStr"/>
+      <c r="M344" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:59:42 UTC</t>
+        </is>
+      </c>
+      <c r="N344" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/45799576/2025-toyota-rav4-hybrid-xle-in-indianapolis</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="7" t="inlineStr">
+        <is>
+          <t>42066516</t>
+        </is>
+      </c>
+      <c r="B345" s="7" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 PRIME SE</t>
+        </is>
+      </c>
+      <c r="C345" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D345" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E345" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F345" s="7" t="n"/>
+      <c r="G345" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H345" s="8" t="n"/>
+      <c r="I345" s="7" t="n"/>
+      <c r="J345" s="7" t="inlineStr"/>
+      <c r="K345" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L345" s="7" t="inlineStr"/>
+      <c r="M345" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-16 19:59:42 UTC</t>
+        </is>
+      </c>
+      <c r="N345" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/42066516/2023-toyota-rav4-prime-se-sc-north-charleston</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N345"/>
+  <dimension ref="A1:N347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18586,6 +18586,98 @@
       <c r="N345" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/42066516/2023-toyota-rav4-prime-se-sc-north-charleston</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="5" t="inlineStr">
+        <is>
+          <t>46318986</t>
+        </is>
+      </c>
+      <c r="B346" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C346" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D346" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E346" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F346" s="5" t="n"/>
+      <c r="G346" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H346" s="6" t="n"/>
+      <c r="I346" s="5" t="n"/>
+      <c r="J346" s="5" t="inlineStr"/>
+      <c r="K346" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L346" s="5" t="inlineStr"/>
+      <c r="M346" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:53:46 UTC</t>
+        </is>
+      </c>
+      <c r="N346" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46318986/2025-toyota-rav4-hybrid-xle-nc-raleigh</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="7" t="inlineStr">
+        <is>
+          <t>46183856</t>
+        </is>
+      </c>
+      <c r="B347" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C347" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D347" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E347" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F347" s="7" t="n"/>
+      <c r="G347" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H347" s="8" t="n"/>
+      <c r="I347" s="7" t="n"/>
+      <c r="J347" s="7" t="inlineStr"/>
+      <c r="K347" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L347" s="7" t="inlineStr"/>
+      <c r="M347" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-16 22:53:46 UTC</t>
+        </is>
+      </c>
+      <c r="N347" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46183856/2025-toyota-rav4-le-nc-mebane</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N358"/>
+  <dimension ref="A1:N359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19196,6 +19196,52 @@
       <c r="N358" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/45475626/clean-title-2025-toyota-rav4-le-ct-hartford-springfield</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="7" t="inlineStr">
+        <is>
+          <t>46394256</t>
+        </is>
+      </c>
+      <c r="B359" s="7" t="inlineStr">
+        <is>
+          <t>2022 TOYOTA RAV4 HYBRID XSE</t>
+        </is>
+      </c>
+      <c r="C359" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D359" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E359" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F359" s="7" t="n"/>
+      <c r="G359" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H359" s="8" t="n"/>
+      <c r="I359" s="7" t="n"/>
+      <c r="J359" s="7" t="inlineStr"/>
+      <c r="K359" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L359" s="7" t="inlineStr"/>
+      <c r="M359" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-18 05:23:55 UTC</t>
+        </is>
+      </c>
+      <c r="N359" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46394256/2022-toyota-rav4-hybrid-xse-ca-hayward</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N359"/>
+  <dimension ref="A1:N363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19242,6 +19242,194 @@
       <c r="N359" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/46394256/2022-toyota-rav4-hybrid-xse-ca-hayward</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="5" t="inlineStr">
+        <is>
+          <t>46771116</t>
+        </is>
+      </c>
+      <c r="B360" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C360" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D360" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E360" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F360" s="5" t="n"/>
+      <c r="G360" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H360" s="6" t="n"/>
+      <c r="I360" s="5" t="n"/>
+      <c r="J360" s="5" t="inlineStr"/>
+      <c r="K360" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L360" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-24 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="M360" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18 15:56:43 UTC</t>
+        </is>
+      </c>
+      <c r="N360" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46771116/2025-toyota-rav4-hybrid-xle-ny-newburgh</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="7" t="inlineStr">
+        <is>
+          <t>46551806</t>
+        </is>
+      </c>
+      <c r="B361" s="7" t="inlineStr">
+        <is>
+          <t>2026 TOYOTA RAV4 WOODLAND</t>
+        </is>
+      </c>
+      <c r="C361" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D361" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E361" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F361" s="7" t="n"/>
+      <c r="G361" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H361" s="8" t="n"/>
+      <c r="I361" s="7" t="n"/>
+      <c r="J361" s="7" t="inlineStr"/>
+      <c r="K361" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L361" s="7" t="inlineStr"/>
+      <c r="M361" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-18 15:56:43 UTC</t>
+        </is>
+      </c>
+      <c r="N361" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46551806/2026-toyota-rav4-woodland-ri-exeter</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="5" t="inlineStr">
+        <is>
+          <t>46438866</t>
+        </is>
+      </c>
+      <c r="B362" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LIMITED</t>
+        </is>
+      </c>
+      <c r="C362" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D362" s="6" t="inlineStr">
+        <is>
+          <t>Engine Start Program</t>
+        </is>
+      </c>
+      <c r="E362" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F362" s="5" t="n"/>
+      <c r="G362" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" s="6" t="n"/>
+      <c r="I362" s="5" t="n"/>
+      <c r="J362" s="5" t="inlineStr"/>
+      <c r="K362" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L362" s="5" t="inlineStr"/>
+      <c r="M362" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18 15:56:43 UTC</t>
+        </is>
+      </c>
+      <c r="N362" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46438866/2025-toyota-rav4-limited-fl-ft-pierce</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="7" t="inlineStr">
+        <is>
+          <t>46193396</t>
+        </is>
+      </c>
+      <c r="B363" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LIMITED</t>
+        </is>
+      </c>
+      <c r="C363" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D363" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E363" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F363" s="7" t="n"/>
+      <c r="G363" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H363" s="8" t="n"/>
+      <c r="I363" s="7" t="n"/>
+      <c r="J363" s="7" t="inlineStr"/>
+      <c r="K363" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L363" s="7" t="inlineStr"/>
+      <c r="M363" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-18 15:56:43 UTC</t>
+        </is>
+      </c>
+      <c r="N363" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46193396/2025-toyota-rav4-limited-al-mobile</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N366"/>
+  <dimension ref="A1:N372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19568,6 +19568,282 @@
       <c r="N366" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/46154766/2025-toyota-rav4-plug-in-hybrid-xse-oh-columbus</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="7" t="inlineStr">
+        <is>
+          <t>46714166</t>
+        </is>
+      </c>
+      <c r="B367" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C367" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D367" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E367" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F367" s="7" t="n"/>
+      <c r="G367" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H367" s="8" t="n"/>
+      <c r="I367" s="7" t="n"/>
+      <c r="J367" s="7" t="inlineStr"/>
+      <c r="K367" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L367" s="7" t="inlineStr"/>
+      <c r="M367" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-18 22:02:53 UTC</t>
+        </is>
+      </c>
+      <c r="N367" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46714166/2024-toyota-rav4-hybrid-xle-premium-ab-edmonton</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="5" t="inlineStr">
+        <is>
+          <t>46612406</t>
+        </is>
+      </c>
+      <c r="B368" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID LE</t>
+        </is>
+      </c>
+      <c r="C368" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D368" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E368" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F368" s="5" t="n"/>
+      <c r="G368" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H368" s="6" t="n"/>
+      <c r="I368" s="5" t="n"/>
+      <c r="J368" s="5" t="inlineStr"/>
+      <c r="K368" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L368" s="5" t="inlineStr"/>
+      <c r="M368" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18 22:02:53 UTC</t>
+        </is>
+      </c>
+      <c r="N368" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46612406/2024-toyota-rav4-hybrid-le-ma-north-boston</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="7" t="inlineStr">
+        <is>
+          <t>46420316</t>
+        </is>
+      </c>
+      <c r="B369" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID LE</t>
+        </is>
+      </c>
+      <c r="C369" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D369" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E369" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F369" s="7" t="n"/>
+      <c r="G369" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H369" s="8" t="n"/>
+      <c r="I369" s="7" t="n"/>
+      <c r="J369" s="7" t="inlineStr"/>
+      <c r="K369" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L369" s="7" t="inlineStr"/>
+      <c r="M369" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-18 22:02:53 UTC</t>
+        </is>
+      </c>
+      <c r="N369" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46420316/2024-toyota-rav4-hybrid-le-nc-lumberton</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="5" t="inlineStr">
+        <is>
+          <t>46245216</t>
+        </is>
+      </c>
+      <c r="B370" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C370" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D370" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E370" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F370" s="5" t="n"/>
+      <c r="G370" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H370" s="6" t="n"/>
+      <c r="I370" s="5" t="n"/>
+      <c r="J370" s="5" t="inlineStr"/>
+      <c r="K370" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L370" s="5" t="inlineStr"/>
+      <c r="M370" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18 22:02:53 UTC</t>
+        </is>
+      </c>
+      <c r="N370" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46245216/2025-toyota-rav4-hybrid-xle-nh-candia</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="7" t="inlineStr">
+        <is>
+          <t>46166256</t>
+        </is>
+      </c>
+      <c r="B371" s="7" t="inlineStr">
+        <is>
+          <t>2022 TOYOTA RAV4 LIMITED</t>
+        </is>
+      </c>
+      <c r="C371" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D371" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E371" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F371" s="7" t="n"/>
+      <c r="G371" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H371" s="8" t="n"/>
+      <c r="I371" s="7" t="n"/>
+      <c r="J371" s="7" t="inlineStr"/>
+      <c r="K371" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L371" s="7" t="inlineStr"/>
+      <c r="M371" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-18 22:02:53 UTC</t>
+        </is>
+      </c>
+      <c r="N371" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46166256/2022-toyota-rav4-limited-wa-spanaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="5" t="inlineStr">
+        <is>
+          <t>46151496</t>
+        </is>
+      </c>
+      <c r="B372" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C372" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D372" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E372" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F372" s="5" t="n"/>
+      <c r="G372" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H372" s="6" t="n"/>
+      <c r="I372" s="5" t="n"/>
+      <c r="J372" s="5" t="inlineStr"/>
+      <c r="K372" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L372" s="5" t="inlineStr"/>
+      <c r="M372" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18 22:02:53 UTC</t>
+        </is>
+      </c>
+      <c r="N372" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46151496/2025-toyota-rav4-hybrid-xle-il-southern-illinois</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N372"/>
+  <dimension ref="A1:N373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19844,6 +19844,52 @@
       <c r="N372" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/46151496/2025-toyota-rav4-hybrid-xle-il-southern-illinois</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="7" t="inlineStr">
+        <is>
+          <t>46527156</t>
+        </is>
+      </c>
+      <c r="B373" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C373" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D373" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E373" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F373" s="7" t="n"/>
+      <c r="G373" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H373" s="8" t="n"/>
+      <c r="I373" s="7" t="n"/>
+      <c r="J373" s="7" t="inlineStr"/>
+      <c r="K373" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L373" s="7" t="inlineStr"/>
+      <c r="M373" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-19 05:17:27 UTC</t>
+        </is>
+      </c>
+      <c r="N373" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46527156/2025-toyota-rav4-hybrid-xle-wa-spanaway</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N374"/>
+  <dimension ref="A1:N378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19940,6 +19940,190 @@
       <c r="N374" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/97991205/clean-title-2024-toyota-rav4-le-fl-miami-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="7" t="inlineStr">
+        <is>
+          <t>46581916</t>
+        </is>
+      </c>
+      <c r="B375" s="7" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 LIMITED</t>
+        </is>
+      </c>
+      <c r="C375" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D375" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E375" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F375" s="7" t="n"/>
+      <c r="G375" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H375" s="8" t="n"/>
+      <c r="I375" s="7" t="n"/>
+      <c r="J375" s="7" t="inlineStr"/>
+      <c r="K375" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L375" s="7" t="inlineStr"/>
+      <c r="M375" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-19 18:01:04 UTC</t>
+        </is>
+      </c>
+      <c r="N375" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46581916/2023-toyota-rav4-limited-ks-kansas-city</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="5" t="inlineStr">
+        <is>
+          <t>46451956</t>
+        </is>
+      </c>
+      <c r="B376" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C376" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D376" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E376" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F376" s="5" t="n"/>
+      <c r="G376" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H376" s="6" t="n"/>
+      <c r="I376" s="5" t="n"/>
+      <c r="J376" s="5" t="inlineStr"/>
+      <c r="K376" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L376" s="5" t="inlineStr"/>
+      <c r="M376" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-19 18:01:04 UTC</t>
+        </is>
+      </c>
+      <c r="N376" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46451956/2025-toyota-rav4-xle-pa-harrisburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="7" t="inlineStr">
+        <is>
+          <t>46443906</t>
+        </is>
+      </c>
+      <c r="B377" s="7" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 HYBRID XSE</t>
+        </is>
+      </c>
+      <c r="C377" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D377" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E377" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F377" s="7" t="n"/>
+      <c r="G377" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H377" s="8" t="n"/>
+      <c r="I377" s="7" t="n"/>
+      <c r="J377" s="7" t="inlineStr"/>
+      <c r="K377" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L377" s="7" t="inlineStr"/>
+      <c r="M377" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-19 18:01:04 UTC</t>
+        </is>
+      </c>
+      <c r="N377" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46443906/2023-toyota-rav4-hybrid-xse-me-lyman</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="5" t="inlineStr">
+        <is>
+          <t>46355596</t>
+        </is>
+      </c>
+      <c r="B378" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C378" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D378" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E378" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F378" s="5" t="n"/>
+      <c r="G378" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H378" s="6" t="n"/>
+      <c r="I378" s="5" t="n"/>
+      <c r="J378" s="5" t="inlineStr"/>
+      <c r="K378" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L378" s="5" t="inlineStr"/>
+      <c r="M378" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-19 18:01:04 UTC</t>
+        </is>
+      </c>
+      <c r="N378" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46355596/2024-toyota-rav4-hybrid-xle-premium-mn-minneapolis-north</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N381"/>
+  <dimension ref="A1:N385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20262,6 +20262,194 @@
       <c r="N381" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/46134676/2024-toyota-rav4-xle-tx-dallas</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="5" t="inlineStr">
+        <is>
+          <t>78555685</t>
+        </is>
+      </c>
+      <c r="B382" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C382" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D382" s="6" t="inlineStr">
+        <is>
+          <t>Engine Start Program</t>
+        </is>
+      </c>
+      <c r="E382" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F382" s="5" t="n"/>
+      <c r="G382" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H382" s="6" t="n"/>
+      <c r="I382" s="5" t="n"/>
+      <c r="J382" s="5" t="inlineStr"/>
+      <c r="K382" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L382" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-24 16:00 UTC</t>
+        </is>
+      </c>
+      <c r="M382" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:32:48 UTC</t>
+        </is>
+      </c>
+      <c r="N382" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/78555685/clean-title-2025-toyota-rav4-hybrid-xle-fl-miami-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="7" t="inlineStr">
+        <is>
+          <t>46984986</t>
+        </is>
+      </c>
+      <c r="B383" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C383" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D383" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E383" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F383" s="7" t="n"/>
+      <c r="G383" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H383" s="8" t="n"/>
+      <c r="I383" s="7" t="n"/>
+      <c r="J383" s="7" t="inlineStr"/>
+      <c r="K383" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L383" s="7" t="inlineStr"/>
+      <c r="M383" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:32:48 UTC</t>
+        </is>
+      </c>
+      <c r="N383" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46984986/2024-toyota-rav4-xle-mi-flint</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="5" t="inlineStr">
+        <is>
+          <t>46599206</t>
+        </is>
+      </c>
+      <c r="B384" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C384" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D384" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E384" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F384" s="5" t="n"/>
+      <c r="G384" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H384" s="6" t="n"/>
+      <c r="I384" s="5" t="n"/>
+      <c r="J384" s="5" t="inlineStr"/>
+      <c r="K384" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L384" s="5" t="inlineStr"/>
+      <c r="M384" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:32:48 UTC</t>
+        </is>
+      </c>
+      <c r="N384" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46599206/2024-toyota-rav4-hybrid-xle-on-toronto</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="7" t="inlineStr">
+        <is>
+          <t>45690406</t>
+        </is>
+      </c>
+      <c r="B385" s="7" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C385" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D385" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E385" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F385" s="7" t="n"/>
+      <c r="G385" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H385" s="8" t="n"/>
+      <c r="I385" s="7" t="n"/>
+      <c r="J385" s="7" t="inlineStr"/>
+      <c r="K385" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L385" s="7" t="inlineStr"/>
+      <c r="M385" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:32:48 UTC</t>
+        </is>
+      </c>
+      <c r="N385" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/45690406/2023-toyota-rav4-xle-ny-long-island</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N392"/>
+  <dimension ref="A1:N393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20772,6 +20772,52 @@
       <c r="N392" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/46935236/2025-toyota-rav4-hybrid-xle-premium-ca-fresno</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="7" t="inlineStr">
+        <is>
+          <t>46733086</t>
+        </is>
+      </c>
+      <c r="B393" s="7" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 HYBRID XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C393" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D393" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E393" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F393" s="7" t="n"/>
+      <c r="G393" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H393" s="8" t="n"/>
+      <c r="I393" s="7" t="n"/>
+      <c r="J393" s="7" t="inlineStr"/>
+      <c r="K393" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L393" s="7" t="inlineStr"/>
+      <c r="M393" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-21 13:54:56 UTC</t>
+        </is>
+      </c>
+      <c r="N393" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46733086/2023-toyota-rav4-hybrid-xle-premium-il-chicago-south</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N393"/>
+  <dimension ref="A1:N396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20818,6 +20818,144 @@
       <c r="N393" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/46733086/2023-toyota-rav4-hybrid-xle-premium-il-chicago-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="5" t="inlineStr">
+        <is>
+          <t>47044666</t>
+        </is>
+      </c>
+      <c r="B394" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C394" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D394" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E394" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F394" s="5" t="n"/>
+      <c r="G394" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H394" s="6" t="n"/>
+      <c r="I394" s="5" t="n"/>
+      <c r="J394" s="5" t="inlineStr"/>
+      <c r="K394" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L394" s="5" t="inlineStr"/>
+      <c r="M394" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-23 15:40:46 UTC</t>
+        </is>
+      </c>
+      <c r="N394" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47044666/2025-toyota-rav4-le-ga-cartersville</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="7" t="inlineStr">
+        <is>
+          <t>46658226</t>
+        </is>
+      </c>
+      <c r="B395" s="7" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 PRIME XSE</t>
+        </is>
+      </c>
+      <c r="C395" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D395" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E395" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F395" s="7" t="n"/>
+      <c r="G395" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H395" s="8" t="n"/>
+      <c r="I395" s="7" t="n"/>
+      <c r="J395" s="7" t="inlineStr"/>
+      <c r="K395" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L395" s="7" t="inlineStr"/>
+      <c r="M395" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-23 15:40:46 UTC</t>
+        </is>
+      </c>
+      <c r="N395" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46658226/2023-toyota-rav4-prime-xse-il-chicago-north</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="5" t="inlineStr">
+        <is>
+          <t>42005866</t>
+        </is>
+      </c>
+      <c r="B396" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C396" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D396" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E396" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F396" s="5" t="n"/>
+      <c r="G396" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H396" s="6" t="n"/>
+      <c r="I396" s="5" t="n"/>
+      <c r="J396" s="5" t="inlineStr"/>
+      <c r="K396" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L396" s="5" t="inlineStr"/>
+      <c r="M396" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-23 15:40:46 UTC</t>
+        </is>
+      </c>
+      <c r="N396" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/42005866/2025-toyota-rav4-xle-ct-hartford</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N402"/>
+  <dimension ref="A1:N406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21232,6 +21232,194 @@
       <c r="N402" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/47251846/2025-toyota-rav4-xle-premium-pa-philadelphia</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="7" t="inlineStr">
+        <is>
+          <t>78560955</t>
+        </is>
+      </c>
+      <c r="B403" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C403" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D403" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E403" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F403" s="7" t="n"/>
+      <c r="G403" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H403" s="8" t="n"/>
+      <c r="I403" s="7" t="n"/>
+      <c r="J403" s="7" t="inlineStr"/>
+      <c r="K403" s="7" t="inlineStr">
+        <is>
+          <t>✅ NLR</t>
+        </is>
+      </c>
+      <c r="L403" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-23 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="M403" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-24 20:01:27 UTC</t>
+        </is>
+      </c>
+      <c r="N403" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/78560955/salvage-2025-toyota-rav4-hybrid-xle-premium-ga-atlanta-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="5" t="inlineStr">
+        <is>
+          <t>47271386</t>
+        </is>
+      </c>
+      <c r="B404" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C404" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D404" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E404" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F404" s="5" t="n"/>
+      <c r="G404" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H404" s="6" t="n"/>
+      <c r="I404" s="5" t="n"/>
+      <c r="J404" s="5" t="inlineStr"/>
+      <c r="K404" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L404" s="5" t="inlineStr"/>
+      <c r="M404" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-24 20:01:27 UTC</t>
+        </is>
+      </c>
+      <c r="N404" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47271386/2024-toyota-rav4-xle-premium-sc-spartanburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="7" t="inlineStr">
+        <is>
+          <t>47126946</t>
+        </is>
+      </c>
+      <c r="B405" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C405" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D405" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E405" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F405" s="7" t="n"/>
+      <c r="G405" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H405" s="8" t="n"/>
+      <c r="I405" s="7" t="n"/>
+      <c r="J405" s="7" t="inlineStr"/>
+      <c r="K405" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L405" s="7" t="inlineStr"/>
+      <c r="M405" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-24 20:01:27 UTC</t>
+        </is>
+      </c>
+      <c r="N405" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47126946/2025-toyota-rav4-le-ma-south-boston</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="5" t="inlineStr">
+        <is>
+          <t>46505176</t>
+        </is>
+      </c>
+      <c r="B406" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XSE</t>
+        </is>
+      </c>
+      <c r="C406" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D406" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E406" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F406" s="5" t="n"/>
+      <c r="G406" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H406" s="6" t="n"/>
+      <c r="I406" s="5" t="n"/>
+      <c r="J406" s="5" t="inlineStr"/>
+      <c r="K406" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L406" s="5" t="inlineStr"/>
+      <c r="M406" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-24 20:01:27 UTC</t>
+        </is>
+      </c>
+      <c r="N406" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46505176/2025-toyota-rav4-hybrid-xse-ok-oklahoma-city</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N407"/>
+  <dimension ref="A1:N409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21466,6 +21466,98 @@
       <c r="N407" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/47031126/2025-toyota-rav4-xle-mn-minneapolis-north</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="5" t="inlineStr">
+        <is>
+          <t>47575066</t>
+        </is>
+      </c>
+      <c r="B408" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XSE</t>
+        </is>
+      </c>
+      <c r="C408" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D408" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E408" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F408" s="5" t="n"/>
+      <c r="G408" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H408" s="6" t="n"/>
+      <c r="I408" s="5" t="n"/>
+      <c r="J408" s="5" t="inlineStr"/>
+      <c r="K408" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L408" s="5" t="inlineStr"/>
+      <c r="M408" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:17:23 UTC</t>
+        </is>
+      </c>
+      <c r="N408" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47575066/2025-toyota-rav4-hybrid-xse-or-portland-north</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="7" t="inlineStr">
+        <is>
+          <t>47290066</t>
+        </is>
+      </c>
+      <c r="B409" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C409" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D409" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E409" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F409" s="7" t="n"/>
+      <c r="G409" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H409" s="8" t="n"/>
+      <c r="I409" s="7" t="n"/>
+      <c r="J409" s="7" t="inlineStr"/>
+      <c r="K409" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L409" s="7" t="inlineStr"/>
+      <c r="M409" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:17:23 UTC</t>
+        </is>
+      </c>
+      <c r="N409" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47290066/2025-toyota-rav4-xle-ut-salt-lake-city</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N409"/>
+  <dimension ref="A1:N414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21558,6 +21558,240 @@
       <c r="N409" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/47290066/2025-toyota-rav4-xle-ut-salt-lake-city</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="5" t="inlineStr">
+        <is>
+          <t>46641616</t>
+        </is>
+      </c>
+      <c r="B410" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C410" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D410" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E410" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F410" s="5" t="n"/>
+      <c r="G410" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H410" s="6" t="n"/>
+      <c r="I410" s="5" t="n"/>
+      <c r="J410" s="5" t="inlineStr"/>
+      <c r="K410" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L410" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 16:00 UTC</t>
+        </is>
+      </c>
+      <c r="M410" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-25 15:53:08 UTC</t>
+        </is>
+      </c>
+      <c r="N410" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46641616/clean-title-2025-toyota-rav4-xle-premium-fl-orlando-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="7" t="inlineStr">
+        <is>
+          <t>47448776</t>
+        </is>
+      </c>
+      <c r="B411" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C411" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D411" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E411" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F411" s="7" t="n"/>
+      <c r="G411" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H411" s="8" t="n"/>
+      <c r="I411" s="7" t="n"/>
+      <c r="J411" s="7" t="inlineStr"/>
+      <c r="K411" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L411" s="7" t="inlineStr"/>
+      <c r="M411" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-25 15:53:08 UTC</t>
+        </is>
+      </c>
+      <c r="N411" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47448776/2025-toyota-rav4-xle-ga-atlanta-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="5" t="inlineStr">
+        <is>
+          <t>47053706</t>
+        </is>
+      </c>
+      <c r="B412" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C412" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D412" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E412" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F412" s="5" t="n"/>
+      <c r="G412" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H412" s="6" t="n"/>
+      <c r="I412" s="5" t="n"/>
+      <c r="J412" s="5" t="inlineStr"/>
+      <c r="K412" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L412" s="5" t="inlineStr"/>
+      <c r="M412" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-25 15:53:08 UTC</t>
+        </is>
+      </c>
+      <c r="N412" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47053706/2025-toyota-rav4-xle-il-chicago-north</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="7" t="inlineStr">
+        <is>
+          <t>46440566</t>
+        </is>
+      </c>
+      <c r="B413" s="7" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C413" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D413" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E413" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F413" s="7" t="n"/>
+      <c r="G413" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H413" s="8" t="n"/>
+      <c r="I413" s="7" t="n"/>
+      <c r="J413" s="7" t="inlineStr"/>
+      <c r="K413" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L413" s="7" t="inlineStr"/>
+      <c r="M413" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-25 15:53:08 UTC</t>
+        </is>
+      </c>
+      <c r="N413" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46440566/2023-toyota-rav4-xle-qc-montreal</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="5" t="inlineStr">
+        <is>
+          <t>45841366</t>
+        </is>
+      </c>
+      <c r="B414" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C414" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D414" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E414" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F414" s="5" t="n"/>
+      <c r="G414" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H414" s="6" t="n"/>
+      <c r="I414" s="5" t="n"/>
+      <c r="J414" s="5" t="inlineStr"/>
+      <c r="K414" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L414" s="5" t="inlineStr"/>
+      <c r="M414" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-25 15:53:08 UTC</t>
+        </is>
+      </c>
+      <c r="N414" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/45841366/2025-toyota-rav4-hybrid-xle-il-chicago-north</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N418"/>
+  <dimension ref="A1:N422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21980,6 +21980,190 @@
       <c r="N418" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/47303646/2025-toyota-rav4-hybrid-limited-tx-waco</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="7" t="inlineStr">
+        <is>
+          <t>47813816</t>
+        </is>
+      </c>
+      <c r="B419" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID XSE</t>
+        </is>
+      </c>
+      <c r="C419" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D419" s="8" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E419" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F419" s="7" t="n"/>
+      <c r="G419" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H419" s="8" t="n"/>
+      <c r="I419" s="7" t="n"/>
+      <c r="J419" s="7" t="inlineStr"/>
+      <c r="K419" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L419" s="7" t="inlineStr"/>
+      <c r="M419" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-26 15:58:34 UTC</t>
+        </is>
+      </c>
+      <c r="N419" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47813816/2024-toyota-rav4-hybrid-xse-ca-sun-valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="5" t="inlineStr">
+        <is>
+          <t>47639686</t>
+        </is>
+      </c>
+      <c r="B420" s="5" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 HYBRID XSE</t>
+        </is>
+      </c>
+      <c r="C420" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D420" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E420" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F420" s="5" t="n"/>
+      <c r="G420" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H420" s="6" t="n"/>
+      <c r="I420" s="5" t="n"/>
+      <c r="J420" s="5" t="inlineStr"/>
+      <c r="K420" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L420" s="5" t="inlineStr"/>
+      <c r="M420" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-26 15:58:34 UTC</t>
+        </is>
+      </c>
+      <c r="N420" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47639686/2023-toyota-rav4-hybrid-xse-ks-kansas-city</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="7" t="inlineStr">
+        <is>
+          <t>47589836</t>
+        </is>
+      </c>
+      <c r="B421" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 LIMITED</t>
+        </is>
+      </c>
+      <c r="C421" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D421" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E421" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F421" s="7" t="n"/>
+      <c r="G421" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H421" s="8" t="n"/>
+      <c r="I421" s="7" t="n"/>
+      <c r="J421" s="7" t="inlineStr"/>
+      <c r="K421" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L421" s="7" t="inlineStr"/>
+      <c r="M421" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-26 15:58:34 UTC</t>
+        </is>
+      </c>
+      <c r="N421" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47589836/2024-toyota-rav4-limited-vt-rutland</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="5" t="inlineStr">
+        <is>
+          <t>47301046</t>
+        </is>
+      </c>
+      <c r="B422" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID LE</t>
+        </is>
+      </c>
+      <c r="C422" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D422" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E422" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F422" s="5" t="n"/>
+      <c r="G422" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H422" s="6" t="n"/>
+      <c r="I422" s="5" t="n"/>
+      <c r="J422" s="5" t="inlineStr"/>
+      <c r="K422" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L422" s="5" t="inlineStr"/>
+      <c r="M422" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-26 15:58:34 UTC</t>
+        </is>
+      </c>
+      <c r="N422" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47301046/2025-toyota-rav4-hybrid-le-nc-raleigh</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N429"/>
+  <dimension ref="A1:N435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22494,6 +22494,282 @@
       <c r="N429" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/47539716/2023-toyota-rav4-xle-ct-hartford</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="5" t="inlineStr">
+        <is>
+          <t>47905276</t>
+        </is>
+      </c>
+      <c r="B430" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 PLUG-IN HYBRID SE</t>
+        </is>
+      </c>
+      <c r="C430" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D430" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E430" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F430" s="5" t="n"/>
+      <c r="G430" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H430" s="6" t="n"/>
+      <c r="I430" s="5" t="n"/>
+      <c r="J430" s="5" t="inlineStr"/>
+      <c r="K430" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L430" s="5" t="inlineStr"/>
+      <c r="M430" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:53:31 UTC</t>
+        </is>
+      </c>
+      <c r="N430" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47905276/2025-toyota-rav4-plug-in-hybrid-se-ca-rancho-cucamonga</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="7" t="inlineStr">
+        <is>
+          <t>47623956</t>
+        </is>
+      </c>
+      <c r="B431" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 PRIME SE</t>
+        </is>
+      </c>
+      <c r="C431" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D431" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E431" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F431" s="7" t="n"/>
+      <c r="G431" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H431" s="8" t="n"/>
+      <c r="I431" s="7" t="n"/>
+      <c r="J431" s="7" t="inlineStr"/>
+      <c r="K431" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L431" s="7" t="inlineStr"/>
+      <c r="M431" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:53:31 UTC</t>
+        </is>
+      </c>
+      <c r="N431" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47623956/2024-toyota-rav4-prime-se-wa-spanaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="5" t="inlineStr">
+        <is>
+          <t>47576726</t>
+        </is>
+      </c>
+      <c r="B432" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C432" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D432" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E432" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F432" s="5" t="n"/>
+      <c r="G432" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H432" s="6" t="n"/>
+      <c r="I432" s="5" t="n"/>
+      <c r="J432" s="5" t="inlineStr"/>
+      <c r="K432" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L432" s="5" t="inlineStr"/>
+      <c r="M432" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:53:31 UTC</t>
+        </is>
+      </c>
+      <c r="N432" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47576726/2025-toyota-rav4-xle-sc-spartanburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="7" t="inlineStr">
+        <is>
+          <t>47539016</t>
+        </is>
+      </c>
+      <c r="B433" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 PRIME XSE</t>
+        </is>
+      </c>
+      <c r="C433" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D433" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E433" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F433" s="7" t="n"/>
+      <c r="G433" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H433" s="8" t="n"/>
+      <c r="I433" s="7" t="n"/>
+      <c r="J433" s="7" t="inlineStr"/>
+      <c r="K433" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L433" s="7" t="inlineStr"/>
+      <c r="M433" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:53:31 UTC</t>
+        </is>
+      </c>
+      <c r="N433" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47539016/2024-toyota-rav4-prime-xse-ny-long-island</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="5" t="inlineStr">
+        <is>
+          <t>47414626</t>
+        </is>
+      </c>
+      <c r="B434" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID LE</t>
+        </is>
+      </c>
+      <c r="C434" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D434" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E434" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F434" s="5" t="n"/>
+      <c r="G434" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H434" s="6" t="n"/>
+      <c r="I434" s="5" t="n"/>
+      <c r="J434" s="5" t="inlineStr"/>
+      <c r="K434" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L434" s="5" t="inlineStr"/>
+      <c r="M434" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:53:31 UTC</t>
+        </is>
+      </c>
+      <c r="N434" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47414626/2025-toyota-rav4-hybrid-le-ny-albany</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="7" t="inlineStr">
+        <is>
+          <t>47342786</t>
+        </is>
+      </c>
+      <c r="B435" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID LIMITED</t>
+        </is>
+      </c>
+      <c r="C435" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D435" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E435" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F435" s="7" t="n"/>
+      <c r="G435" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H435" s="8" t="n"/>
+      <c r="I435" s="7" t="n"/>
+      <c r="J435" s="7" t="inlineStr"/>
+      <c r="K435" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L435" s="7" t="inlineStr"/>
+      <c r="M435" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:53:31 UTC</t>
+        </is>
+      </c>
+      <c r="N435" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47342786/2024-toyota-rav4-hybrid-limited-il-chicago-north</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N435"/>
+  <dimension ref="A1:N437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22770,6 +22770,102 @@
       <c r="N435" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/47342786/2024-toyota-rav4-hybrid-limited-il-chicago-north</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="5" t="inlineStr">
+        <is>
+          <t>47158636</t>
+        </is>
+      </c>
+      <c r="B436" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C436" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D436" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E436" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F436" s="5" t="n"/>
+      <c r="G436" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H436" s="6" t="n"/>
+      <c r="I436" s="5" t="n"/>
+      <c r="J436" s="5" t="inlineStr"/>
+      <c r="K436" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L436" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 16:00 UTC</t>
+        </is>
+      </c>
+      <c r="M436" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:01:16 UTC</t>
+        </is>
+      </c>
+      <c r="N436" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47158636/clean-title-2025-toyota-rav4-xle-fl-miami-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="7" t="inlineStr">
+        <is>
+          <t>47872086</t>
+        </is>
+      </c>
+      <c r="B437" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C437" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D437" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E437" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F437" s="7" t="n"/>
+      <c r="G437" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H437" s="8" t="n"/>
+      <c r="I437" s="7" t="n"/>
+      <c r="J437" s="7" t="inlineStr"/>
+      <c r="K437" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L437" s="7" t="inlineStr"/>
+      <c r="M437" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:01:16 UTC</t>
+        </is>
+      </c>
+      <c r="N437" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47872086/2025-toyota-rav4-hybrid-xle-pa-philadelphia</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N437"/>
+  <dimension ref="A1:N438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22866,6 +22866,52 @@
       <c r="N437" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/47872086/2025-toyota-rav4-hybrid-xle-pa-philadelphia</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="5" t="inlineStr">
+        <is>
+          <t>47834266</t>
+        </is>
+      </c>
+      <c r="B438" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C438" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D438" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E438" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F438" s="5" t="n"/>
+      <c r="G438" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H438" s="6" t="n"/>
+      <c r="I438" s="5" t="n"/>
+      <c r="J438" s="5" t="inlineStr"/>
+      <c r="K438" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L438" s="5" t="inlineStr"/>
+      <c r="M438" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-28 05:15:53 UTC</t>
+        </is>
+      </c>
+      <c r="N438" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47834266/2024-toyota-rav4-le-ca-san-jose</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N438"/>
+  <dimension ref="A1:N439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22912,6 +22912,52 @@
       <c r="N438" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/47834266/2024-toyota-rav4-le-ca-san-jose</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="7" t="inlineStr">
+        <is>
+          <t>47883446</t>
+        </is>
+      </c>
+      <c r="B439" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C439" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D439" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E439" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F439" s="7" t="n"/>
+      <c r="G439" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H439" s="8" t="n"/>
+      <c r="I439" s="7" t="n"/>
+      <c r="J439" s="7" t="inlineStr"/>
+      <c r="K439" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L439" s="7" t="inlineStr"/>
+      <c r="M439" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-30 12:05:08 UTC</t>
+        </is>
+      </c>
+      <c r="N439" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47883446/2025-toyota-rav4-hybrid-xle-fl-ocala</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N445"/>
+  <dimension ref="A1:N451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23238,6 +23238,282 @@
       <c r="N445" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/47336816/2025-toyota-rav4-xle-on-toronto</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="5" t="inlineStr">
+        <is>
+          <t>48214626</t>
+        </is>
+      </c>
+      <c r="B446" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID SE</t>
+        </is>
+      </c>
+      <c r="C446" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D446" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E446" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F446" s="5" t="n"/>
+      <c r="G446" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H446" s="6" t="n"/>
+      <c r="I446" s="5" t="n"/>
+      <c r="J446" s="5" t="inlineStr"/>
+      <c r="K446" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L446" s="5" t="inlineStr"/>
+      <c r="M446" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30 23:01:48 UTC</t>
+        </is>
+      </c>
+      <c r="N446" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48214626/2024-toyota-rav4-hybrid-se-pa-philadelphia</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="7" t="inlineStr">
+        <is>
+          <t>48091316</t>
+        </is>
+      </c>
+      <c r="B447" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C447" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D447" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E447" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F447" s="7" t="n"/>
+      <c r="G447" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H447" s="8" t="n"/>
+      <c r="I447" s="7" t="n"/>
+      <c r="J447" s="7" t="inlineStr"/>
+      <c r="K447" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L447" s="7" t="inlineStr"/>
+      <c r="M447" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-30 23:01:48 UTC</t>
+        </is>
+      </c>
+      <c r="N447" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48091316/2025-toyota-rav4-xle-ca-van-nuys</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="5" t="inlineStr">
+        <is>
+          <t>48039796</t>
+        </is>
+      </c>
+      <c r="B448" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XSE</t>
+        </is>
+      </c>
+      <c r="C448" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D448" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E448" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F448" s="5" t="n"/>
+      <c r="G448" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H448" s="6" t="n"/>
+      <c r="I448" s="5" t="n"/>
+      <c r="J448" s="5" t="inlineStr"/>
+      <c r="K448" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L448" s="5" t="inlineStr"/>
+      <c r="M448" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30 23:01:48 UTC</t>
+        </is>
+      </c>
+      <c r="N448" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48039796/2025-toyota-rav4-hybrid-xse-tx-north-austin</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="7" t="inlineStr">
+        <is>
+          <t>48002486</t>
+        </is>
+      </c>
+      <c r="B449" s="7" t="inlineStr">
+        <is>
+          <t>2022 TOYOTA RAV4 LIMITED</t>
+        </is>
+      </c>
+      <c r="C449" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D449" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E449" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F449" s="7" t="n"/>
+      <c r="G449" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H449" s="8" t="n"/>
+      <c r="I449" s="7" t="n"/>
+      <c r="J449" s="7" t="inlineStr"/>
+      <c r="K449" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L449" s="7" t="inlineStr"/>
+      <c r="M449" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-30 23:01:48 UTC</t>
+        </is>
+      </c>
+      <c r="N449" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48002486/2022-toyota-rav4-limited-co-colorado-springs</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="5" t="inlineStr">
+        <is>
+          <t>48002356</t>
+        </is>
+      </c>
+      <c r="B450" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C450" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D450" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E450" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F450" s="5" t="n"/>
+      <c r="G450" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H450" s="6" t="n"/>
+      <c r="I450" s="5" t="n"/>
+      <c r="J450" s="5" t="inlineStr"/>
+      <c r="K450" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L450" s="5" t="inlineStr"/>
+      <c r="M450" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30 23:01:48 UTC</t>
+        </is>
+      </c>
+      <c r="N450" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48002356/2025-toyota-rav4-xle-premium-ca-sacramento</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="7" t="inlineStr">
+        <is>
+          <t>47882156</t>
+        </is>
+      </c>
+      <c r="B451" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID WOODLAND EDITION</t>
+        </is>
+      </c>
+      <c r="C451" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D451" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E451" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F451" s="7" t="n"/>
+      <c r="G451" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H451" s="8" t="n"/>
+      <c r="I451" s="7" t="n"/>
+      <c r="J451" s="7" t="inlineStr"/>
+      <c r="K451" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L451" s="7" t="inlineStr"/>
+      <c r="M451" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-30 23:01:48 UTC</t>
+        </is>
+      </c>
+      <c r="N451" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47882156/2025-toyota-rav4-hybrid-woodland-edition-al-tanner</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N451"/>
+  <dimension ref="A1:N452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23514,6 +23514,52 @@
       <c r="N451" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/47882156/2025-toyota-rav4-hybrid-woodland-edition-al-tanner</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="5" t="inlineStr">
+        <is>
+          <t>46897616</t>
+        </is>
+      </c>
+      <c r="B452" s="5" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C452" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D452" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E452" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F452" s="5" t="n"/>
+      <c r="G452" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H452" s="6" t="n"/>
+      <c r="I452" s="5" t="n"/>
+      <c r="J452" s="5" t="inlineStr"/>
+      <c r="K452" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L452" s="5" t="inlineStr"/>
+      <c r="M452" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 05:57:35 UTC</t>
+        </is>
+      </c>
+      <c r="N452" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46897616/2023-toyota-rav4-hybrid-xle-wa-north-seattle</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N452"/>
+  <dimension ref="A1:N457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23560,6 +23560,244 @@
       <c r="N452" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/46897616/2023-toyota-rav4-hybrid-xle-wa-north-seattle</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="7" t="inlineStr">
+        <is>
+          <t>79434275</t>
+        </is>
+      </c>
+      <c r="B453" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 PRIME XSE</t>
+        </is>
+      </c>
+      <c r="C453" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D453" s="8" t="inlineStr">
+        <is>
+          <t>Engine Start Program</t>
+        </is>
+      </c>
+      <c r="E453" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F453" s="7" t="n"/>
+      <c r="G453" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H453" s="8" t="n"/>
+      <c r="I453" s="7" t="n"/>
+      <c r="J453" s="7" t="inlineStr"/>
+      <c r="K453" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L453" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-02 16:00 UTC</t>
+        </is>
+      </c>
+      <c r="M453" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:54:13 UTC</t>
+        </is>
+      </c>
+      <c r="N453" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/79434275/clean-title-2024-toyota-rav4-prime-xse-ca-van-nuys</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="5" t="inlineStr">
+        <is>
+          <t>74815135</t>
+        </is>
+      </c>
+      <c r="B454" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C454" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D454" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E454" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F454" s="5" t="n"/>
+      <c r="G454" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H454" s="6" t="n"/>
+      <c r="I454" s="5" t="n"/>
+      <c r="J454" s="5" t="inlineStr"/>
+      <c r="K454" s="5" t="inlineStr">
+        <is>
+          <t>✅ NLR</t>
+        </is>
+      </c>
+      <c r="L454" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:00 UTC</t>
+        </is>
+      </c>
+      <c r="M454" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:54:13 UTC</t>
+        </is>
+      </c>
+      <c r="N454" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/74815135/salvage-2024-toyota-rav4-xle-ab-edmonton</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="7" t="inlineStr">
+        <is>
+          <t>48168456</t>
+        </is>
+      </c>
+      <c r="B455" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C455" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D455" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E455" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F455" s="7" t="n"/>
+      <c r="G455" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H455" s="8" t="n"/>
+      <c r="I455" s="7" t="n"/>
+      <c r="J455" s="7" t="inlineStr"/>
+      <c r="K455" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L455" s="7" t="inlineStr"/>
+      <c r="M455" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:54:13 UTC</t>
+        </is>
+      </c>
+      <c r="N455" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48168456/2025-toyota-rav4-hybrid-xle-ga-savannah</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="5" t="inlineStr">
+        <is>
+          <t>48163386</t>
+        </is>
+      </c>
+      <c r="B456" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID SE</t>
+        </is>
+      </c>
+      <c r="C456" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D456" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E456" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F456" s="5" t="n"/>
+      <c r="G456" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H456" s="6" t="n"/>
+      <c r="I456" s="5" t="n"/>
+      <c r="J456" s="5" t="inlineStr"/>
+      <c r="K456" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L456" s="5" t="inlineStr"/>
+      <c r="M456" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:54:13 UTC</t>
+        </is>
+      </c>
+      <c r="N456" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48163386/2025-toyota-rav4-hybrid-se-ga-fairburn</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="7" t="inlineStr">
+        <is>
+          <t>47931996</t>
+        </is>
+      </c>
+      <c r="B457" s="7" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C457" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D457" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E457" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F457" s="7" t="n"/>
+      <c r="G457" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H457" s="8" t="n"/>
+      <c r="I457" s="7" t="n"/>
+      <c r="J457" s="7" t="inlineStr"/>
+      <c r="K457" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L457" s="7" t="inlineStr"/>
+      <c r="M457" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-31 15:54:13 UTC</t>
+        </is>
+      </c>
+      <c r="N457" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47931996/2023-toyota-rav4-xle-qc-montreal</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N460"/>
+  <dimension ref="A1:N463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23936,6 +23936,144 @@
       <c r="N460" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/48155826/2025-toyota-rav4-hybrid-xle-ut-salt-lake-city</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="7" t="inlineStr">
+        <is>
+          <t>48186436</t>
+        </is>
+      </c>
+      <c r="B461" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C461" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D461" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E461" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F461" s="7" t="n"/>
+      <c r="G461" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H461" s="8" t="n"/>
+      <c r="I461" s="7" t="n"/>
+      <c r="J461" s="7" t="inlineStr"/>
+      <c r="K461" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L461" s="7" t="inlineStr"/>
+      <c r="M461" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:54:02 UTC</t>
+        </is>
+      </c>
+      <c r="N461" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48186436/2025-toyota-rav4-hybrid-xle-ma-north-boston</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="5" t="inlineStr">
+        <is>
+          <t>47979546</t>
+        </is>
+      </c>
+      <c r="B462" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XSE</t>
+        </is>
+      </c>
+      <c r="C462" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D462" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E462" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F462" s="5" t="n"/>
+      <c r="G462" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H462" s="6" t="n"/>
+      <c r="I462" s="5" t="n"/>
+      <c r="J462" s="5" t="inlineStr"/>
+      <c r="K462" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L462" s="5" t="inlineStr"/>
+      <c r="M462" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:54:02 UTC</t>
+        </is>
+      </c>
+      <c r="N462" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47979546/2025-toyota-rav4-hybrid-xse-tn-knoxville</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="7" t="inlineStr">
+        <is>
+          <t>47564996</t>
+        </is>
+      </c>
+      <c r="B463" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C463" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D463" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E463" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F463" s="7" t="n"/>
+      <c r="G463" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H463" s="8" t="n"/>
+      <c r="I463" s="7" t="n"/>
+      <c r="J463" s="7" t="inlineStr"/>
+      <c r="K463" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L463" s="7" t="inlineStr"/>
+      <c r="M463" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-31 22:54:02 UTC</t>
+        </is>
+      </c>
+      <c r="N463" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47564996/2024-toyota-rav4-le-oh-columbus</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N469"/>
+  <dimension ref="A1:N475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24350,6 +24350,290 @@
       <c r="N469" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/46767066/2024-toyota-rav4-hybrid-limited-il-chicago-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="5" t="inlineStr">
+        <is>
+          <t>46560566</t>
+        </is>
+      </c>
+      <c r="B470" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4</t>
+        </is>
+      </c>
+      <c r="C470" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D470" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E470" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F470" s="5" t="n"/>
+      <c r="G470" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H470" s="6" t="n"/>
+      <c r="I470" s="5" t="n"/>
+      <c r="J470" s="5" t="inlineStr"/>
+      <c r="K470" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L470" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="M470" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 23:04:55 UTC</t>
+        </is>
+      </c>
+      <c r="N470" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46560566/salvage-2025-toyota-rav4-nj-trenton</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="7" t="inlineStr">
+        <is>
+          <t>46744106</t>
+        </is>
+      </c>
+      <c r="B471" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C471" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D471" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E471" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F471" s="7" t="n"/>
+      <c r="G471" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H471" s="8" t="n"/>
+      <c r="I471" s="7" t="n"/>
+      <c r="J471" s="7" t="inlineStr"/>
+      <c r="K471" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L471" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-04 15:00 UTC</t>
+        </is>
+      </c>
+      <c r="M471" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-01 23:04:55 UTC</t>
+        </is>
+      </c>
+      <c r="N471" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46744106/salvage-2025-toyota-rav4-le-ca-san-diego</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="5" t="inlineStr">
+        <is>
+          <t>48498546</t>
+        </is>
+      </c>
+      <c r="B472" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C472" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D472" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E472" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F472" s="5" t="n"/>
+      <c r="G472" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H472" s="6" t="n"/>
+      <c r="I472" s="5" t="n"/>
+      <c r="J472" s="5" t="inlineStr"/>
+      <c r="K472" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L472" s="5" t="inlineStr"/>
+      <c r="M472" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 23:04:55 UTC</t>
+        </is>
+      </c>
+      <c r="N472" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48498546/2024-toyota-rav4-xle-premium-ca-sun-valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="7" t="inlineStr">
+        <is>
+          <t>48295136</t>
+        </is>
+      </c>
+      <c r="B473" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID LE</t>
+        </is>
+      </c>
+      <c r="C473" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D473" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E473" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F473" s="7" t="n"/>
+      <c r="G473" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H473" s="8" t="n"/>
+      <c r="I473" s="7" t="n"/>
+      <c r="J473" s="7" t="inlineStr"/>
+      <c r="K473" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L473" s="7" t="inlineStr"/>
+      <c r="M473" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-01 23:04:55 UTC</t>
+        </is>
+      </c>
+      <c r="N473" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48295136/2025-toyota-rav4-hybrid-le-in-cicero</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="5" t="inlineStr">
+        <is>
+          <t>48119816</t>
+        </is>
+      </c>
+      <c r="B474" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C474" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D474" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E474" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F474" s="5" t="n"/>
+      <c r="G474" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H474" s="6" t="n"/>
+      <c r="I474" s="5" t="n"/>
+      <c r="J474" s="5" t="inlineStr"/>
+      <c r="K474" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L474" s="5" t="inlineStr"/>
+      <c r="M474" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01 23:04:55 UTC</t>
+        </is>
+      </c>
+      <c r="N474" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48119816/2025-toyota-rav4-le-ca-san-bernardino</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="7" t="inlineStr">
+        <is>
+          <t>48100886</t>
+        </is>
+      </c>
+      <c r="B475" s="7" t="inlineStr">
+        <is>
+          <t>2022 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C475" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D475" s="8" t="inlineStr">
+        <is>
+          <t>Engine Start Program</t>
+        </is>
+      </c>
+      <c r="E475" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F475" s="7" t="n"/>
+      <c r="G475" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H475" s="8" t="n"/>
+      <c r="I475" s="7" t="n"/>
+      <c r="J475" s="7" t="inlineStr"/>
+      <c r="K475" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L475" s="7" t="inlineStr"/>
+      <c r="M475" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-01 23:04:55 UTC</t>
+        </is>
+      </c>
+      <c r="N475" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48100886/2022-toyota-rav4-xle-premium-tx-mcallen</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N475"/>
+  <dimension ref="A1:N479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24634,6 +24634,190 @@
       <c r="N475" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/48100886/2022-toyota-rav4-xle-premium-tx-mcallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="5" t="inlineStr">
+        <is>
+          <t>48590306</t>
+        </is>
+      </c>
+      <c r="B476" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C476" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D476" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E476" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F476" s="5" t="n"/>
+      <c r="G476" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H476" s="6" t="n"/>
+      <c r="I476" s="5" t="n"/>
+      <c r="J476" s="5" t="inlineStr"/>
+      <c r="K476" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L476" s="5" t="inlineStr"/>
+      <c r="M476" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:38:32 UTC</t>
+        </is>
+      </c>
+      <c r="N476" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48590306/2024-toyota-rav4-xle-ga-cartersville</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="7" t="inlineStr">
+        <is>
+          <t>48333686</t>
+        </is>
+      </c>
+      <c r="B477" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C477" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D477" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E477" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F477" s="7" t="n"/>
+      <c r="G477" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H477" s="8" t="n"/>
+      <c r="I477" s="7" t="n"/>
+      <c r="J477" s="7" t="inlineStr"/>
+      <c r="K477" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L477" s="7" t="inlineStr"/>
+      <c r="M477" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:38:32 UTC</t>
+        </is>
+      </c>
+      <c r="N477" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48333686/2025-toyota-rav4-hybrid-xle-on-cookstown</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="5" t="inlineStr">
+        <is>
+          <t>48076286</t>
+        </is>
+      </c>
+      <c r="B478" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C478" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D478" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E478" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F478" s="5" t="n"/>
+      <c r="G478" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H478" s="6" t="n"/>
+      <c r="I478" s="5" t="n"/>
+      <c r="J478" s="5" t="inlineStr"/>
+      <c r="K478" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L478" s="5" t="inlineStr"/>
+      <c r="M478" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:38:32 UTC</t>
+        </is>
+      </c>
+      <c r="N478" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48076286/2025-toyota-rav4-xle-ok-oklahoma-city</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="7" t="inlineStr">
+        <is>
+          <t>47877396</t>
+        </is>
+      </c>
+      <c r="B479" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C479" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D479" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E479" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F479" s="7" t="n"/>
+      <c r="G479" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H479" s="8" t="n"/>
+      <c r="I479" s="7" t="n"/>
+      <c r="J479" s="7" t="inlineStr"/>
+      <c r="K479" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L479" s="7" t="inlineStr"/>
+      <c r="M479" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:38:32 UTC</t>
+        </is>
+      </c>
+      <c r="N479" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47877396/2025-toyota-rav4-hybrid-xle-premium-va-fredericksburg</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N486"/>
+  <dimension ref="A1:N488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25144,6 +25144,98 @@
       <c r="N486" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/48188396/2023-toyota-rav4-hybrid-se-mi-flint</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="7" t="inlineStr">
+        <is>
+          <t>48740266</t>
+        </is>
+      </c>
+      <c r="B487" s="7" t="inlineStr">
+        <is>
+          <t>2026 TOYOTA RAV4 XSE</t>
+        </is>
+      </c>
+      <c r="C487" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D487" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E487" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F487" s="7" t="n"/>
+      <c r="G487" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H487" s="8" t="n"/>
+      <c r="I487" s="7" t="n"/>
+      <c r="J487" s="7" t="inlineStr"/>
+      <c r="K487" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L487" s="7" t="inlineStr"/>
+      <c r="M487" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:52:28 UTC</t>
+        </is>
+      </c>
+      <c r="N487" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48740266/2026-toyota-rav4-xse-ny-newburgh</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="5" t="inlineStr">
+        <is>
+          <t>48623446</t>
+        </is>
+      </c>
+      <c r="B488" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C488" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D488" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E488" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F488" s="5" t="n"/>
+      <c r="G488" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H488" s="6" t="n"/>
+      <c r="I488" s="5" t="n"/>
+      <c r="J488" s="5" t="inlineStr"/>
+      <c r="K488" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L488" s="5" t="inlineStr"/>
+      <c r="M488" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:52:28 UTC</t>
+        </is>
+      </c>
+      <c r="N488" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48623446/2025-toyota-rav4-xle-me-lyman</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N493"/>
+  <dimension ref="A1:N498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25470,6 +25470,236 @@
       <c r="N493" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/48666926/2025-toyota-rav4-xle-premium-co-denver-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="5" t="inlineStr">
+        <is>
+          <t>48937806</t>
+        </is>
+      </c>
+      <c r="B494" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 LIMITED</t>
+        </is>
+      </c>
+      <c r="C494" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D494" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E494" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F494" s="5" t="n"/>
+      <c r="G494" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H494" s="6" t="n"/>
+      <c r="I494" s="5" t="n"/>
+      <c r="J494" s="5" t="inlineStr"/>
+      <c r="K494" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L494" s="5" t="inlineStr"/>
+      <c r="M494" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 15:51:44 UTC</t>
+        </is>
+      </c>
+      <c r="N494" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48937806/2024-toyota-rav4-limited-tx-houston</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="7" t="inlineStr">
+        <is>
+          <t>48620956</t>
+        </is>
+      </c>
+      <c r="B495" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C495" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D495" s="8" t="inlineStr">
+        <is>
+          <t>Engine Start Program</t>
+        </is>
+      </c>
+      <c r="E495" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F495" s="7" t="n"/>
+      <c r="G495" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H495" s="8" t="n"/>
+      <c r="I495" s="7" t="n"/>
+      <c r="J495" s="7" t="inlineStr"/>
+      <c r="K495" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L495" s="7" t="inlineStr"/>
+      <c r="M495" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-06 15:51:44 UTC</t>
+        </is>
+      </c>
+      <c r="N495" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48620956/2025-toyota-rav4-xle-va-fredericksburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="5" t="inlineStr">
+        <is>
+          <t>48291176</t>
+        </is>
+      </c>
+      <c r="B496" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 TRD OFF-ROAD</t>
+        </is>
+      </c>
+      <c r="C496" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D496" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E496" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F496" s="5" t="n"/>
+      <c r="G496" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H496" s="6" t="n"/>
+      <c r="I496" s="5" t="n"/>
+      <c r="J496" s="5" t="inlineStr"/>
+      <c r="K496" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L496" s="5" t="inlineStr"/>
+      <c r="M496" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 15:51:44 UTC</t>
+        </is>
+      </c>
+      <c r="N496" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48291176/2024-toyota-rav4-trd-off-road-fl-orlando-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="7" t="inlineStr">
+        <is>
+          <t>48144926</t>
+        </is>
+      </c>
+      <c r="B497" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID LE</t>
+        </is>
+      </c>
+      <c r="C497" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D497" s="8" t="inlineStr">
+        <is>
+          <t>Engine Start Program</t>
+        </is>
+      </c>
+      <c r="E497" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F497" s="7" t="n"/>
+      <c r="G497" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H497" s="8" t="n"/>
+      <c r="I497" s="7" t="n"/>
+      <c r="J497" s="7" t="inlineStr"/>
+      <c r="K497" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L497" s="7" t="inlineStr"/>
+      <c r="M497" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-06 15:51:44 UTC</t>
+        </is>
+      </c>
+      <c r="N497" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48144926/2024-toyota-rav4-hybrid-le-ct-hartford</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="5" t="inlineStr">
+        <is>
+          <t>46061976</t>
+        </is>
+      </c>
+      <c r="B498" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C498" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D498" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E498" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F498" s="5" t="n"/>
+      <c r="G498" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H498" s="6" t="n"/>
+      <c r="I498" s="5" t="n"/>
+      <c r="J498" s="5" t="inlineStr"/>
+      <c r="K498" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L498" s="5" t="inlineStr"/>
+      <c r="M498" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06 15:51:44 UTC</t>
+        </is>
+      </c>
+      <c r="N498" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46061976/2024-toyota-rav4-xle-premium-il-chicago-south</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N498"/>
+  <dimension ref="A1:N499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25700,6 +25700,52 @@
       <c r="N498" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/46061976/2024-toyota-rav4-xle-premium-il-chicago-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="7" t="inlineStr">
+        <is>
+          <t>48841616</t>
+        </is>
+      </c>
+      <c r="B499" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C499" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D499" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E499" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F499" s="7" t="n"/>
+      <c r="G499" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H499" s="8" t="n"/>
+      <c r="I499" s="7" t="n"/>
+      <c r="J499" s="7" t="inlineStr"/>
+      <c r="K499" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L499" s="7" t="inlineStr"/>
+      <c r="M499" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-06 19:04:53 UTC</t>
+        </is>
+      </c>
+      <c r="N499" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48841616/2025-toyota-rav4-xle-tx-houston</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N506"/>
+  <dimension ref="A1:N507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26068,6 +26068,52 @@
       <c r="N506" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/48702056/2026-toyota-rav4-limited-az-tucson</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="7" t="inlineStr">
+        <is>
+          <t>49100226</t>
+        </is>
+      </c>
+      <c r="B507" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C507" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D507" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E507" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F507" s="7" t="n"/>
+      <c r="G507" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H507" s="8" t="n"/>
+      <c r="I507" s="7" t="n"/>
+      <c r="J507" s="7" t="inlineStr"/>
+      <c r="K507" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L507" s="7" t="inlineStr"/>
+      <c r="M507" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-07 13:24:05 UTC</t>
+        </is>
+      </c>
+      <c r="N507" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49100226/2025-toyota-rav4-le-ky-louisville</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N513"/>
+  <dimension ref="A1:N516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26390,6 +26390,144 @@
       <c r="N513" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/48945226/2024-toyota-rav4-xle-ut-ogden</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="5" t="inlineStr">
+        <is>
+          <t>49321186</t>
+        </is>
+      </c>
+      <c r="B514" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C514" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D514" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E514" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F514" s="5" t="n"/>
+      <c r="G514" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" s="6" t="n"/>
+      <c r="I514" s="5" t="n"/>
+      <c r="J514" s="5" t="inlineStr"/>
+      <c r="K514" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L514" s="5" t="inlineStr"/>
+      <c r="M514" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-07 21:43:24 UTC</t>
+        </is>
+      </c>
+      <c r="N514" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49321186/2025-toyota-rav4-xle-ga-atlanta-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="7" t="inlineStr">
+        <is>
+          <t>48991086</t>
+        </is>
+      </c>
+      <c r="B515" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C515" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D515" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E515" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F515" s="7" t="n"/>
+      <c r="G515" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H515" s="8" t="n"/>
+      <c r="I515" s="7" t="n"/>
+      <c r="J515" s="7" t="inlineStr"/>
+      <c r="K515" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L515" s="7" t="inlineStr"/>
+      <c r="M515" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-07 21:43:24 UTC</t>
+        </is>
+      </c>
+      <c r="N515" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48991086/2025-toyota-rav4-le-nv-las-vegas</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="5" t="inlineStr">
+        <is>
+          <t>41624986</t>
+        </is>
+      </c>
+      <c r="B516" s="5" t="inlineStr">
+        <is>
+          <t>2022 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C516" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D516" s="6" t="inlineStr">
+        <is>
+          <t>Engine Start Program</t>
+        </is>
+      </c>
+      <c r="E516" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F516" s="5" t="n"/>
+      <c r="G516" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H516" s="6" t="n"/>
+      <c r="I516" s="5" t="n"/>
+      <c r="J516" s="5" t="inlineStr"/>
+      <c r="K516" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L516" s="5" t="inlineStr"/>
+      <c r="M516" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-07 21:43:24 UTC</t>
+        </is>
+      </c>
+      <c r="N516" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/41624986/2022-toyota-rav4-xle-on-toronto</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N518"/>
+  <dimension ref="A1:N519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26620,6 +26620,56 @@
       <c r="N518" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/47999196/2022-toyota-rav4-limited-wa-north-seattle</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="7" t="inlineStr">
+        <is>
+          <t>72873505</t>
+        </is>
+      </c>
+      <c r="B519" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE AWD</t>
+        </is>
+      </c>
+      <c r="C519" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D519" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E519" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F519" s="7" t="n"/>
+      <c r="G519" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H519" s="8" t="n"/>
+      <c r="I519" s="7" t="n"/>
+      <c r="J519" s="7" t="inlineStr"/>
+      <c r="K519" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L519" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-09 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="M519" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-08 05:13:20 UTC</t>
+        </is>
+      </c>
+      <c r="N519" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/72873505/2025-toyota-rav4-hybrid-xle-awd-md-baltimore-east</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N526"/>
+  <dimension ref="A1:N527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26996,6 +26996,52 @@
       <c r="N526" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/49055016/2025-toyota-rav4-xle-ny-buffalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="7" t="inlineStr">
+        <is>
+          <t>49334296</t>
+        </is>
+      </c>
+      <c r="B527" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XSE</t>
+        </is>
+      </c>
+      <c r="C527" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D527" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E527" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F527" s="7" t="n"/>
+      <c r="G527" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H527" s="8" t="n"/>
+      <c r="I527" s="7" t="n"/>
+      <c r="J527" s="7" t="inlineStr"/>
+      <c r="K527" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L527" s="7" t="inlineStr"/>
+      <c r="M527" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-09 02:33:42 UTC</t>
+        </is>
+      </c>
+      <c r="N527" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49334296/2024-toyota-rav4-xse-ca-san-jose</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N528"/>
+  <dimension ref="A1:N530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27088,6 +27088,98 @@
       <c r="N528" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/49176816/2025-toyota-rav4-le-fl-tampa-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="7" t="inlineStr">
+        <is>
+          <t>49475886</t>
+        </is>
+      </c>
+      <c r="B529" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C529" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D529" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E529" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F529" s="7" t="n"/>
+      <c r="G529" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H529" s="8" t="n"/>
+      <c r="I529" s="7" t="n"/>
+      <c r="J529" s="7" t="inlineStr"/>
+      <c r="K529" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L529" s="7" t="inlineStr"/>
+      <c r="M529" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-09 16:19:55 UTC</t>
+        </is>
+      </c>
+      <c r="N529" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49475886/2025-toyota-rav4-xle-tx-houston</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="5" t="inlineStr">
+        <is>
+          <t>49380126</t>
+        </is>
+      </c>
+      <c r="B530" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 ADVENTURE</t>
+        </is>
+      </c>
+      <c r="C530" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D530" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E530" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F530" s="5" t="n"/>
+      <c r="G530" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H530" s="6" t="n"/>
+      <c r="I530" s="5" t="n"/>
+      <c r="J530" s="5" t="inlineStr"/>
+      <c r="K530" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L530" s="5" t="inlineStr"/>
+      <c r="M530" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09 16:19:55 UTC</t>
+        </is>
+      </c>
+      <c r="N530" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49380126/2025-toyota-rav4-adventure-nb-moncton</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N530"/>
+  <dimension ref="A1:N531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27180,6 +27180,56 @@
       <c r="N530" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/49380126/2025-toyota-rav4-adventure-nb-moncton</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="7" t="inlineStr">
+        <is>
+          <t>78871735</t>
+        </is>
+      </c>
+      <c r="B531" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 PRIME XSE</t>
+        </is>
+      </c>
+      <c r="C531" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D531" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E531" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F531" s="7" t="n"/>
+      <c r="G531" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H531" s="8" t="n"/>
+      <c r="I531" s="7" t="n"/>
+      <c r="J531" s="7" t="inlineStr"/>
+      <c r="K531" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L531" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:00 UTC</t>
+        </is>
+      </c>
+      <c r="M531" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-09 19:11:08 UTC</t>
+        </is>
+      </c>
+      <c r="N531" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/78871735/salvage-2024-toyota-rav4-prime-xse-ca-san-diego</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N533"/>
+  <dimension ref="A1:N538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27322,6 +27322,236 @@
       <c r="N533" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/49604436/2025-toyota-rav4-xle-ak-anchorage</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="5" t="inlineStr">
+        <is>
+          <t>49631666</t>
+        </is>
+      </c>
+      <c r="B534" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C534" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D534" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E534" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F534" s="5" t="n"/>
+      <c r="G534" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H534" s="6" t="n"/>
+      <c r="I534" s="5" t="n"/>
+      <c r="J534" s="5" t="inlineStr"/>
+      <c r="K534" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L534" s="5" t="inlineStr"/>
+      <c r="M534" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10 21:40:40 UTC</t>
+        </is>
+      </c>
+      <c r="N534" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49631666/2024-toyota-rav4-xle-va-fredericksburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="7" t="inlineStr">
+        <is>
+          <t>49591296</t>
+        </is>
+      </c>
+      <c r="B535" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C535" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D535" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E535" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F535" s="7" t="n"/>
+      <c r="G535" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H535" s="8" t="n"/>
+      <c r="I535" s="7" t="n"/>
+      <c r="J535" s="7" t="inlineStr"/>
+      <c r="K535" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L535" s="7" t="inlineStr"/>
+      <c r="M535" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-10 21:40:40 UTC</t>
+        </is>
+      </c>
+      <c r="N535" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49591296/2024-toyota-rav4-hybrid-xle-ma-north-boston</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="5" t="inlineStr">
+        <is>
+          <t>49436636</t>
+        </is>
+      </c>
+      <c r="B536" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C536" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D536" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E536" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F536" s="5" t="n"/>
+      <c r="G536" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H536" s="6" t="n"/>
+      <c r="I536" s="5" t="n"/>
+      <c r="J536" s="5" t="inlineStr"/>
+      <c r="K536" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L536" s="5" t="inlineStr"/>
+      <c r="M536" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10 21:40:40 UTC</t>
+        </is>
+      </c>
+      <c r="N536" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49436636/2024-toyota-rav4-hybrid-xle-dc-washington-dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="7" t="inlineStr">
+        <is>
+          <t>48948186</t>
+        </is>
+      </c>
+      <c r="B537" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C537" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D537" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E537" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F537" s="7" t="n"/>
+      <c r="G537" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H537" s="8" t="n"/>
+      <c r="I537" s="7" t="n"/>
+      <c r="J537" s="7" t="inlineStr"/>
+      <c r="K537" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L537" s="7" t="inlineStr"/>
+      <c r="M537" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-10 21:40:40 UTC</t>
+        </is>
+      </c>
+      <c r="N537" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48948186/2024-toyota-rav4-hybrid-xle-va-richmond</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="5" t="inlineStr">
+        <is>
+          <t>47799536</t>
+        </is>
+      </c>
+      <c r="B538" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C538" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D538" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E538" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F538" s="5" t="n"/>
+      <c r="G538" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H538" s="6" t="n"/>
+      <c r="I538" s="5" t="n"/>
+      <c r="J538" s="5" t="inlineStr"/>
+      <c r="K538" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L538" s="5" t="inlineStr"/>
+      <c r="M538" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10 21:40:40 UTC</t>
+        </is>
+      </c>
+      <c r="N538" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47799536/2025-toyota-rav4-hybrid-xle-premium-ny-rochester</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N540"/>
+  <dimension ref="A1:N542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27652,6 +27652,98 @@
       <c r="N540" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/49283906/clean-title-2025-toyota-rav4-xle-oh-cleveland-west</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="7" t="inlineStr">
+        <is>
+          <t>49728946</t>
+        </is>
+      </c>
+      <c r="B541" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XSE</t>
+        </is>
+      </c>
+      <c r="C541" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D541" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E541" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F541" s="7" t="n"/>
+      <c r="G541" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H541" s="8" t="n"/>
+      <c r="I541" s="7" t="n"/>
+      <c r="J541" s="7" t="inlineStr"/>
+      <c r="K541" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L541" s="7" t="inlineStr"/>
+      <c r="M541" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-13 16:16:15 UTC</t>
+        </is>
+      </c>
+      <c r="N541" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49728946/2025-toyota-rav4-hybrid-xse-il-southern-illinois</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="5" t="inlineStr">
+        <is>
+          <t>48960836</t>
+        </is>
+      </c>
+      <c r="B542" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C542" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D542" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E542" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F542" s="5" t="n"/>
+      <c r="G542" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H542" s="6" t="n"/>
+      <c r="I542" s="5" t="n"/>
+      <c r="J542" s="5" t="inlineStr"/>
+      <c r="K542" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L542" s="5" t="inlineStr"/>
+      <c r="M542" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13 16:16:15 UTC</t>
+        </is>
+      </c>
+      <c r="N542" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48960836/2024-toyota-rav4-xle-fl-tampa-south</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N545"/>
+  <dimension ref="A1:N547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27886,6 +27886,98 @@
       <c r="N545" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/48739036/2024-toyota-rav4-hybrid-xle-on-toronto</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="5" t="inlineStr">
+        <is>
+          <t>49869596</t>
+        </is>
+      </c>
+      <c r="B546" s="5" t="inlineStr">
+        <is>
+          <t>2026 TOYOTA RAV4 WOODLAND</t>
+        </is>
+      </c>
+      <c r="C546" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D546" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E546" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F546" s="5" t="n"/>
+      <c r="G546" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H546" s="6" t="n"/>
+      <c r="I546" s="5" t="n"/>
+      <c r="J546" s="5" t="inlineStr"/>
+      <c r="K546" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L546" s="5" t="inlineStr"/>
+      <c r="M546" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:47:14 UTC</t>
+        </is>
+      </c>
+      <c r="N546" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49869596/2026-toyota-rav4-woodland-in-indianapolis</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="7" t="inlineStr">
+        <is>
+          <t>49286886</t>
+        </is>
+      </c>
+      <c r="B547" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C547" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D547" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E547" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F547" s="7" t="n"/>
+      <c r="G547" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H547" s="8" t="n"/>
+      <c r="I547" s="7" t="n"/>
+      <c r="J547" s="7" t="inlineStr"/>
+      <c r="K547" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L547" s="7" t="inlineStr"/>
+      <c r="M547" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:47:14 UTC</t>
+        </is>
+      </c>
+      <c r="N547" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49286886/2025-toyota-rav4-hybrid-xle-ny-syracuse</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N547"/>
+  <dimension ref="A1:N548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27978,6 +27978,52 @@
       <c r="N547" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/49286886/2025-toyota-rav4-hybrid-xle-ny-syracuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="5" t="inlineStr">
+        <is>
+          <t>49909246</t>
+        </is>
+      </c>
+      <c r="B548" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C548" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D548" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E548" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F548" s="5" t="n"/>
+      <c r="G548" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H548" s="6" t="n"/>
+      <c r="I548" s="5" t="n"/>
+      <c r="J548" s="5" t="inlineStr"/>
+      <c r="K548" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L548" s="5" t="inlineStr"/>
+      <c r="M548" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-14 16:10:10 UTC</t>
+        </is>
+      </c>
+      <c r="N548" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49909246/2024-toyota-rav4-xle-premium-co-denver-central</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N548"/>
+  <dimension ref="A1:N549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28024,6 +28024,52 @@
       <c r="N548" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/49909246/2024-toyota-rav4-xle-premium-co-denver-central</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="7" t="inlineStr">
+        <is>
+          <t>49404296</t>
+        </is>
+      </c>
+      <c r="B549" s="7" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 SE</t>
+        </is>
+      </c>
+      <c r="C549" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D549" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E549" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F549" s="7" t="n"/>
+      <c r="G549" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H549" s="8" t="n"/>
+      <c r="I549" s="7" t="n"/>
+      <c r="J549" s="7" t="inlineStr"/>
+      <c r="K549" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L549" s="7" t="inlineStr"/>
+      <c r="M549" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-14 19:20:07 UTC</t>
+        </is>
+      </c>
+      <c r="N549" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49404296/2024-toyota-rav4-se-tx-north-austin</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N551"/>
+  <dimension ref="A1:N552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28166,6 +28166,52 @@
       <c r="N551" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/41623476/salvage-2025-toyota-rav4-hybrid-xle-ca-napa</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="5" t="inlineStr">
+        <is>
+          <t>48846476</t>
+        </is>
+      </c>
+      <c r="B552" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C552" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D552" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E552" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F552" s="5" t="n"/>
+      <c r="G552" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H552" s="6" t="n"/>
+      <c r="I552" s="5" t="n"/>
+      <c r="J552" s="5" t="inlineStr"/>
+      <c r="K552" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L552" s="5" t="inlineStr"/>
+      <c r="M552" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-15 13:42:48 UTC</t>
+        </is>
+      </c>
+      <c r="N552" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/48846476/2025-toyota-rav4-xle-premium-sc-north-charleston</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N559"/>
+  <dimension ref="A1:N562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28542,6 +28542,144 @@
       <c r="N559" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/49737136/2025-toyota-rav4-xle-tx-ft-worth</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="5" t="inlineStr">
+        <is>
+          <t>50399816</t>
+        </is>
+      </c>
+      <c r="B560" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C560" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D560" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E560" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F560" s="5" t="n"/>
+      <c r="G560" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H560" s="6" t="n"/>
+      <c r="I560" s="5" t="n"/>
+      <c r="J560" s="5" t="inlineStr"/>
+      <c r="K560" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L560" s="5" t="inlineStr"/>
+      <c r="M560" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:51:33 UTC</t>
+        </is>
+      </c>
+      <c r="N560" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50399816/2024-toyota-rav4-xle-tx-dallas</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="7" t="inlineStr">
+        <is>
+          <t>50269866</t>
+        </is>
+      </c>
+      <c r="B561" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C561" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D561" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E561" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F561" s="7" t="n"/>
+      <c r="G561" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H561" s="8" t="n"/>
+      <c r="I561" s="7" t="n"/>
+      <c r="J561" s="7" t="inlineStr"/>
+      <c r="K561" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L561" s="7" t="inlineStr"/>
+      <c r="M561" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:51:33 UTC</t>
+        </is>
+      </c>
+      <c r="N561" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50269866/2025-toyota-rav4-xle-ma-south-boston</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="5" t="inlineStr">
+        <is>
+          <t>50001976</t>
+        </is>
+      </c>
+      <c r="B562" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C562" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D562" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E562" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F562" s="5" t="n"/>
+      <c r="G562" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H562" s="6" t="n"/>
+      <c r="I562" s="5" t="n"/>
+      <c r="J562" s="5" t="inlineStr"/>
+      <c r="K562" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L562" s="5" t="inlineStr"/>
+      <c r="M562" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 13:51:33 UTC</t>
+        </is>
+      </c>
+      <c r="N562" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50001976/2025-toyota-rav4-le-fl-tampa-south</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N562"/>
+  <dimension ref="A1:N564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28680,6 +28680,98 @@
       <c r="N562" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/50001976/2025-toyota-rav4-le-fl-tampa-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="7" t="inlineStr">
+        <is>
+          <t>49994326</t>
+        </is>
+      </c>
+      <c r="B563" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C563" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D563" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E563" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F563" s="7" t="n"/>
+      <c r="G563" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H563" s="8" t="n"/>
+      <c r="I563" s="7" t="n"/>
+      <c r="J563" s="7" t="inlineStr"/>
+      <c r="K563" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L563" s="7" t="inlineStr"/>
+      <c r="M563" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:24:20 UTC</t>
+        </is>
+      </c>
+      <c r="N563" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49994326/2025-toyota-rav4-xle-premium-ca-fresno</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="5" t="inlineStr">
+        <is>
+          <t>49702636</t>
+        </is>
+      </c>
+      <c r="B564" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C564" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D564" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E564" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F564" s="5" t="n"/>
+      <c r="G564" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H564" s="6" t="n"/>
+      <c r="I564" s="5" t="n"/>
+      <c r="J564" s="5" t="inlineStr"/>
+      <c r="K564" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L564" s="5" t="inlineStr"/>
+      <c r="M564" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 16:24:20 UTC</t>
+        </is>
+      </c>
+      <c r="N564" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49702636/2025-toyota-rav4-xle-fl-orlando-south</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N564"/>
+  <dimension ref="A1:N566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28772,6 +28772,98 @@
       <c r="N564" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/49702636/2025-toyota-rav4-xle-fl-orlando-south</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="7" t="inlineStr">
+        <is>
+          <t>49949206</t>
+        </is>
+      </c>
+      <c r="B565" s="7" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 LIMITED</t>
+        </is>
+      </c>
+      <c r="C565" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D565" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E565" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F565" s="7" t="n"/>
+      <c r="G565" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H565" s="8" t="n"/>
+      <c r="I565" s="7" t="n"/>
+      <c r="J565" s="7" t="inlineStr"/>
+      <c r="K565" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L565" s="7" t="inlineStr"/>
+      <c r="M565" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-16 19:19:34 UTC</t>
+        </is>
+      </c>
+      <c r="N565" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49949206/2023-toyota-rav4-limited-co-denver</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="5" t="inlineStr">
+        <is>
+          <t>49535526</t>
+        </is>
+      </c>
+      <c r="B566" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C566" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D566" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E566" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F566" s="5" t="n"/>
+      <c r="G566" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H566" s="6" t="n"/>
+      <c r="I566" s="5" t="n"/>
+      <c r="J566" s="5" t="inlineStr"/>
+      <c r="K566" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L566" s="5" t="inlineStr"/>
+      <c r="M566" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 19:19:34 UTC</t>
+        </is>
+      </c>
+      <c r="N566" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49535526/2025-toyota-rav4-le-ca-sun-valley</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N566"/>
+  <dimension ref="A1:N569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28864,6 +28864,148 @@
       <c r="N566" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/49535526/2025-toyota-rav4-le-ca-sun-valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="7" t="inlineStr">
+        <is>
+          <t>46188236</t>
+        </is>
+      </c>
+      <c r="B567" s="7" t="inlineStr">
+        <is>
+          <t>2022 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C567" s="7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D567" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E567" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F567" s="7" t="n"/>
+      <c r="G567" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H567" s="8" t="n"/>
+      <c r="I567" s="7" t="n"/>
+      <c r="J567" s="7" t="inlineStr"/>
+      <c r="K567" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L567" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="M567" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:46:50 UTC</t>
+        </is>
+      </c>
+      <c r="N567" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/46188236/salvage-2022-toyota-rav4-le-ny-newburgh</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="5" t="inlineStr">
+        <is>
+          <t>50172316</t>
+        </is>
+      </c>
+      <c r="B568" s="5" t="inlineStr">
+        <is>
+          <t>2024 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C568" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D568" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E568" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F568" s="5" t="n"/>
+      <c r="G568" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H568" s="6" t="n"/>
+      <c r="I568" s="5" t="n"/>
+      <c r="J568" s="5" t="inlineStr"/>
+      <c r="K568" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L568" s="5" t="inlineStr"/>
+      <c r="M568" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:46:50 UTC</t>
+        </is>
+      </c>
+      <c r="N568" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50172316/2024-toyota-rav4-hybrid-xle-mi-lansing</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="7" t="inlineStr">
+        <is>
+          <t>49844606</t>
+        </is>
+      </c>
+      <c r="B569" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C569" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D569" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E569" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F569" s="7" t="n"/>
+      <c r="G569" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H569" s="8" t="n"/>
+      <c r="I569" s="7" t="n"/>
+      <c r="J569" s="7" t="inlineStr"/>
+      <c r="K569" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L569" s="7" t="inlineStr"/>
+      <c r="M569" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:46:50 UTC</t>
+        </is>
+      </c>
+      <c r="N569" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49844606/2025-toyota-rav4-hybrid-xle-nv-las-vegas</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N579"/>
+  <dimension ref="A1:N580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29478,6 +29478,52 @@
       <c r="N579" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/50149696/2024-toyota-rav4-hybrid-xle-wa-spanaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="5" t="inlineStr">
+        <is>
+          <t>49582116</t>
+        </is>
+      </c>
+      <c r="B580" s="5" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C580" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D580" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E580" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F580" s="5" t="n"/>
+      <c r="G580" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H580" s="6" t="n"/>
+      <c r="I580" s="5" t="n"/>
+      <c r="J580" s="5" t="inlineStr"/>
+      <c r="K580" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L580" s="5" t="inlineStr"/>
+      <c r="M580" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:44:12 UTC</t>
+        </is>
+      </c>
+      <c r="N580" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49582116/2023-toyota-rav4-xle-nj-glassboro-east</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N580"/>
+  <dimension ref="A1:N583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -29524,6 +29524,144 @@
       <c r="N580" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/49582116/2023-toyota-rav4-xle-nj-glassboro-east</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="7" t="inlineStr">
+        <is>
+          <t>50349946</t>
+        </is>
+      </c>
+      <c r="B581" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C581" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D581" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E581" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F581" s="7" t="n"/>
+      <c r="G581" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H581" s="8" t="n"/>
+      <c r="I581" s="7" t="n"/>
+      <c r="J581" s="7" t="inlineStr"/>
+      <c r="K581" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L581" s="7" t="inlineStr"/>
+      <c r="M581" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-20 13:47:39 UTC</t>
+        </is>
+      </c>
+      <c r="N581" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50349946/2025-toyota-rav4-xle-nj-somerville</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="5" t="inlineStr">
+        <is>
+          <t>49233696</t>
+        </is>
+      </c>
+      <c r="B582" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C582" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D582" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E582" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F582" s="5" t="n"/>
+      <c r="G582" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H582" s="6" t="n"/>
+      <c r="I582" s="5" t="n"/>
+      <c r="J582" s="5" t="inlineStr"/>
+      <c r="K582" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L582" s="5" t="inlineStr"/>
+      <c r="M582" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-20 13:47:39 UTC</t>
+        </is>
+      </c>
+      <c r="N582" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/49233696/2025-toyota-rav4-xle-sc-spartanburg</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="7" t="inlineStr">
+        <is>
+          <t>47525346</t>
+        </is>
+      </c>
+      <c r="B583" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C583" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D583" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E583" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F583" s="7" t="n"/>
+      <c r="G583" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H583" s="8" t="n"/>
+      <c r="I583" s="7" t="n"/>
+      <c r="J583" s="7" t="inlineStr"/>
+      <c r="K583" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L583" s="7" t="inlineStr"/>
+      <c r="M583" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-20 13:47:39 UTC</t>
+        </is>
+      </c>
+      <c r="N583" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/47525346/2025-toyota-rav4-le-on-toronto</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N592"/>
+  <dimension ref="A1:N593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30084,6 +30084,52 @@
       <c r="N592" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/50438446/2025-toyota-rav4-xle-ca-long-beach</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="7" t="inlineStr">
+        <is>
+          <t>50606386</t>
+        </is>
+      </c>
+      <c r="B593" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C593" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D593" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E593" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F593" s="7" t="n"/>
+      <c r="G593" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H593" s="8" t="n"/>
+      <c r="I593" s="7" t="n"/>
+      <c r="J593" s="7" t="inlineStr"/>
+      <c r="K593" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L593" s="7" t="inlineStr"/>
+      <c r="M593" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21 13:47:01 UTC</t>
+        </is>
+      </c>
+      <c r="N593" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50606386/2025-toyota-rav4-xle-ct-hartford-springfield</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N604"/>
+  <dimension ref="A1:N607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30652,6 +30652,144 @@
       <c r="N604" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/50687506/2025-toyota-rav4-xle-il-chicago-north</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="7" t="inlineStr">
+        <is>
+          <t>50954756</t>
+        </is>
+      </c>
+      <c r="B605" s="7" t="inlineStr">
+        <is>
+          <t>2026 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C605" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D605" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E605" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F605" s="7" t="n"/>
+      <c r="G605" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H605" s="8" t="n"/>
+      <c r="I605" s="7" t="n"/>
+      <c r="J605" s="7" t="inlineStr"/>
+      <c r="K605" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L605" s="7" t="inlineStr"/>
+      <c r="M605" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-22 19:17:24 UTC</t>
+        </is>
+      </c>
+      <c r="N605" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50954756/2026-toyota-rav4-xle-premium-me-lyman</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="5" t="inlineStr">
+        <is>
+          <t>50933416</t>
+        </is>
+      </c>
+      <c r="B606" s="5" t="inlineStr">
+        <is>
+          <t>2022 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C606" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D606" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E606" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F606" s="5" t="n"/>
+      <c r="G606" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H606" s="6" t="n"/>
+      <c r="I606" s="5" t="n"/>
+      <c r="J606" s="5" t="inlineStr"/>
+      <c r="K606" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L606" s="5" t="inlineStr"/>
+      <c r="M606" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22 19:17:24 UTC</t>
+        </is>
+      </c>
+      <c r="N606" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50933416/2022-toyota-rav4-xle-tx-waco</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="7" t="inlineStr">
+        <is>
+          <t>50890436</t>
+        </is>
+      </c>
+      <c r="B607" s="7" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C607" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D607" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E607" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F607" s="7" t="n"/>
+      <c r="G607" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H607" s="8" t="n"/>
+      <c r="I607" s="7" t="n"/>
+      <c r="J607" s="7" t="inlineStr"/>
+      <c r="K607" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L607" s="7" t="inlineStr"/>
+      <c r="M607" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-22 19:17:24 UTC</t>
+        </is>
+      </c>
+      <c r="N607" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50890436/2023-toyota-rav4-le-ca-martinez</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N607"/>
+  <dimension ref="A1:N608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30790,6 +30790,56 @@
       <c r="N607" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/50890436/2023-toyota-rav4-le-ca-martinez</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="5" t="inlineStr">
+        <is>
+          <t>69442545</t>
+        </is>
+      </c>
+      <c r="B608" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C608" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D608" s="6" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E608" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F608" s="5" t="n"/>
+      <c r="G608" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H608" s="6" t="n"/>
+      <c r="I608" s="5" t="n"/>
+      <c r="J608" s="5" t="inlineStr"/>
+      <c r="K608" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L608" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:00 UTC</t>
+        </is>
+      </c>
+      <c r="M608" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22 21:53:08 UTC</t>
+        </is>
+      </c>
+      <c r="N608" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/69442545/salvage-2025-toyota-rav4-xle-cn-canadian-affiliates</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N608"/>
+  <dimension ref="A1:N611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30840,6 +30840,144 @@
       <c r="N608" s="5" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/69442545/salvage-2025-toyota-rav4-xle-cn-canadian-affiliates</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="7" t="inlineStr">
+        <is>
+          <t>50577356</t>
+        </is>
+      </c>
+      <c r="B609" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C609" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D609" s="8" t="inlineStr">
+        <is>
+          <t>Engine Start Program</t>
+        </is>
+      </c>
+      <c r="E609" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F609" s="7" t="n"/>
+      <c r="G609" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H609" s="8" t="n"/>
+      <c r="I609" s="7" t="n"/>
+      <c r="J609" s="7" t="inlineStr"/>
+      <c r="K609" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L609" s="7" t="inlineStr"/>
+      <c r="M609" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-23 16:44:44 UTC</t>
+        </is>
+      </c>
+      <c r="N609" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50577356/2025-toyota-rav4-xle-ny-buffalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="5" t="inlineStr">
+        <is>
+          <t>50427066</t>
+        </is>
+      </c>
+      <c r="B610" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C610" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D610" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E610" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F610" s="5" t="n"/>
+      <c r="G610" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H610" s="6" t="n"/>
+      <c r="I610" s="5" t="n"/>
+      <c r="J610" s="5" t="inlineStr"/>
+      <c r="K610" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L610" s="5" t="inlineStr"/>
+      <c r="M610" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23 16:44:44 UTC</t>
+        </is>
+      </c>
+      <c r="N610" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50427066/2025-toyota-rav4-hybrid-xle-ca-van-nuys</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="7" t="inlineStr">
+        <is>
+          <t>50086026</t>
+        </is>
+      </c>
+      <c r="B611" s="7" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 HYBRID XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C611" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D611" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced Vehicles</t>
+        </is>
+      </c>
+      <c r="E611" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F611" s="7" t="n"/>
+      <c r="G611" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H611" s="8" t="n"/>
+      <c r="I611" s="7" t="n"/>
+      <c r="J611" s="7" t="inlineStr"/>
+      <c r="K611" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L611" s="7" t="inlineStr"/>
+      <c r="M611" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-23 16:44:44 UTC</t>
+        </is>
+      </c>
+      <c r="N611" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50086026/2023-toyota-rav4-hybrid-xle-premium-co-denver</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N611"/>
+  <dimension ref="A1:N613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30978,6 +30978,98 @@
       <c r="N611" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/50086026/2023-toyota-rav4-hybrid-xle-premium-co-denver</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="5" t="inlineStr">
+        <is>
+          <t>50950516</t>
+        </is>
+      </c>
+      <c r="B612" s="5" t="inlineStr">
+        <is>
+          <t>2023 TOYOTA RAV4 XLE PREMIUM</t>
+        </is>
+      </c>
+      <c r="C612" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D612" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E612" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F612" s="5" t="n"/>
+      <c r="G612" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H612" s="6" t="n"/>
+      <c r="I612" s="5" t="n"/>
+      <c r="J612" s="5" t="inlineStr"/>
+      <c r="K612" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L612" s="5" t="inlineStr"/>
+      <c r="M612" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23 19:14:34 UTC</t>
+        </is>
+      </c>
+      <c r="N612" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50950516/2023-toyota-rav4-xle-premium-tx-houston-east</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="7" t="inlineStr">
+        <is>
+          <t>50584586</t>
+        </is>
+      </c>
+      <c r="B613" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 XLE</t>
+        </is>
+      </c>
+      <c r="C613" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D613" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E613" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F613" s="7" t="n"/>
+      <c r="G613" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H613" s="8" t="n"/>
+      <c r="I613" s="7" t="n"/>
+      <c r="J613" s="7" t="inlineStr"/>
+      <c r="K613" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L613" s="7" t="inlineStr"/>
+      <c r="M613" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-23 19:14:34 UTC</t>
+        </is>
+      </c>
+      <c r="N613" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50584586/2025-toyota-rav4-xle-tx-houston-east</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N613"/>
+  <dimension ref="A1:N615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31070,6 +31070,98 @@
       <c r="N613" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/50584586/2025-toyota-rav4-xle-tx-houston-east</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="5" t="inlineStr">
+        <is>
+          <t>50766376</t>
+        </is>
+      </c>
+      <c r="B614" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 HYBRID XLE</t>
+        </is>
+      </c>
+      <c r="C614" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D614" s="6" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E614" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F614" s="5" t="n"/>
+      <c r="G614" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H614" s="6" t="n"/>
+      <c r="I614" s="5" t="n"/>
+      <c r="J614" s="5" t="inlineStr"/>
+      <c r="K614" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L614" s="5" t="inlineStr"/>
+      <c r="M614" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-23 21:49:46 UTC</t>
+        </is>
+      </c>
+      <c r="N614" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50766376/2025-toyota-rav4-hybrid-xle-fl-tampa-north</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="7" t="inlineStr">
+        <is>
+          <t>50605246</t>
+        </is>
+      </c>
+      <c r="B615" s="7" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C615" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D615" s="8" t="inlineStr">
+        <is>
+          <t>Runs And Drives</t>
+        </is>
+      </c>
+      <c r="E615" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F615" s="7" t="n"/>
+      <c r="G615" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H615" s="8" t="n"/>
+      <c r="I615" s="7" t="n"/>
+      <c r="J615" s="7" t="inlineStr"/>
+      <c r="K615" s="7" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L615" s="7" t="inlineStr"/>
+      <c r="M615" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-23 21:49:46 UTC</t>
+        </is>
+      </c>
+      <c r="N615" s="7" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50605246/2025-toyota-rav4-le-il-chicago-north</t>
         </is>
       </c>
     </row>

--- a/copart_auctions.xlsx
+++ b/copart_auctions.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N615"/>
+  <dimension ref="A1:N616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31162,6 +31162,52 @@
       <c r="N615" s="7" t="inlineStr">
         <is>
           <t>https://www.copart.com/lot/50605246/2025-toyota-rav4-le-il-chicago-north</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="5" t="inlineStr">
+        <is>
+          <t>50249966</t>
+        </is>
+      </c>
+      <c r="B616" s="5" t="inlineStr">
+        <is>
+          <t>2025 TOYOTA RAV4 LE</t>
+        </is>
+      </c>
+      <c r="C616" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D616" s="6" t="inlineStr">
+        <is>
+          <t>Engine Start Program</t>
+        </is>
+      </c>
+      <c r="E616" s="6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F616" s="5" t="n"/>
+      <c r="G616" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H616" s="6" t="n"/>
+      <c r="I616" s="5" t="n"/>
+      <c r="J616" s="5" t="inlineStr"/>
+      <c r="K616" s="5" t="inlineStr">
+        <is>
+          <t>🔑 Broker</t>
+        </is>
+      </c>
+      <c r="L616" s="5" t="inlineStr"/>
+      <c r="M616" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-24 02:50:40 UTC</t>
+        </is>
+      </c>
+      <c r="N616" s="5" t="inlineStr">
+        <is>
+          <t>https://www.copart.com/lot/50249966/2025-toyota-rav4-le-il-chicago-north</t>
         </is>
       </c>
     </row>
